--- a/ig/nr/3.0.1/StructureDefinition-mesures-observation-pain-severity.xlsx
+++ b/ig/nr/3.0.1/StructureDefinition-mesures-observation-pain-severity.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AP$104</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AP$103</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4031" uniqueCount="668">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3993" uniqueCount="666">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-26T08:11:02+00:00</t>
+    <t>2023-04-26T08:20:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -329,6 +329,10 @@
 </t>
   </si>
   <si>
+    <t xml:space="preserve">ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+</t>
+  </si>
+  <si>
     <t>N/A</t>
   </si>
   <si>
@@ -403,10 +407,6 @@
     <t>Meta.versionId</t>
   </si>
   <si>
-    <t xml:space="preserve">ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-</t>
-  </si>
-  <si>
     <t>Observation.meta.lastUpdated</t>
   </si>
   <si>
@@ -459,14 +459,7 @@
     <t>It is up to the server and/or other infrastructure of policy to determine whether/how these claims are verified and/or updated over time.  The list of profile URLs is a set.</t>
   </si>
   <si>
-    <t xml:space="preserve">value:$this}
-</t>
-  </si>
-  <si>
     <t>Meta.profile</t>
-  </si>
-  <si>
-    <t>Observation.meta.profile:MesObservationPainSeverity</t>
   </si>
   <si>
     <t>Observation.meta.security</t>
@@ -2413,12 +2406,12 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AP104"/>
+  <dimension ref="A1:AP103"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="50.87890625" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="49.3046875" customWidth="true" bestFit="true"/>
     <col min="2" max="2" width="49.3046875" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="27.34375" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="3" max="3" width="27.03125" customWidth="true" bestFit="true" hidden="true"/>
     <col min="4" max="4" width="39.9140625" customWidth="true" bestFit="true" hidden="true"/>
     <col min="5" max="5" width="6.77734375" customWidth="true" bestFit="true"/>
     <col min="6" max="6" width="4.9453125" customWidth="true" bestFit="true"/>
@@ -2840,7 +2833,7 @@
       </c>
       <c r="E4" s="2"/>
       <c r="F4" t="s" s="2">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="G4" t="s" s="2">
         <v>89</v>
@@ -2924,7 +2917,7 @@
         <v>101</v>
       </c>
       <c r="AJ4" t="s" s="2">
-        <v>79</v>
+        <v>102</v>
       </c>
       <c r="AK4" t="s" s="2">
         <v>79</v>
@@ -2936,7 +2929,7 @@
         <v>79</v>
       </c>
       <c r="AN4" t="s" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="AO4" t="s" s="2">
         <v>79</v>
@@ -2947,10 +2940,10 @@
     </row>
     <row r="5" hidden="true">
       <c r="A5" t="s" s="2">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C5" s="2"/>
       <c r="D5" t="s" s="2">
@@ -2973,13 +2966,13 @@
         <v>79</v>
       </c>
       <c r="K5" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="L5" t="s" s="2">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="M5" t="s" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="N5" s="2"/>
       <c r="O5" s="2"/>
@@ -3030,7 +3023,7 @@
         <v>79</v>
       </c>
       <c r="AF5" t="s" s="2">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="AG5" t="s" s="2">
         <v>77</v>
@@ -3054,7 +3047,7 @@
         <v>79</v>
       </c>
       <c r="AN5" t="s" s="2">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="AO5" t="s" s="2">
         <v>79</v>
@@ -3065,14 +3058,14 @@
     </row>
     <row r="6" hidden="true">
       <c r="A6" t="s" s="2">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C6" s="2"/>
       <c r="D6" t="s" s="2">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="E6" s="2"/>
       <c r="F6" t="s" s="2">
@@ -3091,16 +3084,16 @@
         <v>79</v>
       </c>
       <c r="K6" t="s" s="2">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="L6" t="s" s="2">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="M6" t="s" s="2">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="N6" t="s" s="2">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="O6" s="2"/>
       <c r="P6" t="s" s="2">
@@ -3138,19 +3131,19 @@
         <v>79</v>
       </c>
       <c r="AB6" t="s" s="2">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="AC6" t="s" s="2">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="AD6" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AE6" t="s" s="2">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="AF6" t="s" s="2">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="AG6" t="s" s="2">
         <v>77</v>
@@ -3162,7 +3155,7 @@
         <v>101</v>
       </c>
       <c r="AJ6" t="s" s="2">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="AK6" t="s" s="2">
         <v>79</v>
@@ -3174,7 +3167,7 @@
         <v>79</v>
       </c>
       <c r="AN6" t="s" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="AO6" t="s" s="2">
         <v>79</v>
@@ -3185,10 +3178,10 @@
     </row>
     <row r="7" hidden="true">
       <c r="A7" t="s" s="2">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="C7" s="2"/>
       <c r="D7" t="s" s="2">
@@ -3214,13 +3207,13 @@
         <v>91</v>
       </c>
       <c r="L7" t="s" s="2">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="M7" t="s" s="2">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="N7" t="s" s="2">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="O7" s="2"/>
       <c r="P7" t="s" s="2">
@@ -3270,7 +3263,7 @@
         <v>79</v>
       </c>
       <c r="AF7" t="s" s="2">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="AG7" t="s" s="2">
         <v>77</v>
@@ -3282,7 +3275,7 @@
         <v>101</v>
       </c>
       <c r="AJ7" t="s" s="2">
-        <v>125</v>
+        <v>102</v>
       </c>
       <c r="AK7" t="s" s="2">
         <v>79</v>
@@ -3294,7 +3287,7 @@
         <v>79</v>
       </c>
       <c r="AN7" t="s" s="2">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="AO7" t="s" s="2">
         <v>79</v>
@@ -3402,7 +3395,7 @@
         <v>101</v>
       </c>
       <c r="AJ8" t="s" s="2">
-        <v>125</v>
+        <v>102</v>
       </c>
       <c r="AK8" t="s" s="2">
         <v>79</v>
@@ -3414,7 +3407,7 @@
         <v>79</v>
       </c>
       <c r="AN8" t="s" s="2">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="AO8" t="s" s="2">
         <v>79</v>
@@ -3522,7 +3515,7 @@
         <v>101</v>
       </c>
       <c r="AJ9" t="s" s="2">
-        <v>125</v>
+        <v>102</v>
       </c>
       <c r="AK9" t="s" s="2">
         <v>79</v>
@@ -3534,7 +3527,7 @@
         <v>79</v>
       </c>
       <c r="AN9" t="s" s="2">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="AO9" t="s" s="2">
         <v>79</v>
@@ -3556,7 +3549,7 @@
       </c>
       <c r="E10" s="2"/>
       <c r="F10" t="s" s="2">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="G10" t="s" s="2">
         <v>78</v>
@@ -3618,17 +3611,19 @@
         <v>79</v>
       </c>
       <c r="AB10" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AC10" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AD10" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AE10" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AF10" t="s" s="2">
         <v>142</v>
-      </c>
-      <c r="AC10" s="2"/>
-      <c r="AD10" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AE10" t="s" s="2">
-        <v>117</v>
-      </c>
-      <c r="AF10" t="s" s="2">
-        <v>143</v>
       </c>
       <c r="AG10" t="s" s="2">
         <v>77</v>
@@ -3640,7 +3635,7 @@
         <v>101</v>
       </c>
       <c r="AJ10" t="s" s="2">
-        <v>125</v>
+        <v>102</v>
       </c>
       <c r="AK10" t="s" s="2">
         <v>79</v>
@@ -3652,7 +3647,7 @@
         <v>79</v>
       </c>
       <c r="AN10" t="s" s="2">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="AO10" t="s" s="2">
         <v>79</v>
@@ -3663,26 +3658,24 @@
     </row>
     <row r="11" hidden="true">
       <c r="A11" t="s" s="2">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>137</v>
-      </c>
-      <c r="C11" t="s" s="2">
-        <v>7</v>
-      </c>
+        <v>143</v>
+      </c>
+      <c r="C11" s="2"/>
       <c r="D11" t="s" s="2">
         <v>79</v>
       </c>
       <c r="E11" s="2"/>
       <c r="F11" t="s" s="2">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="G11" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="H11" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="I11" t="s" s="2">
         <v>79</v>
@@ -3691,16 +3684,16 @@
         <v>90</v>
       </c>
       <c r="K11" t="s" s="2">
-        <v>138</v>
+        <v>144</v>
       </c>
       <c r="L11" t="s" s="2">
-        <v>139</v>
+        <v>145</v>
       </c>
       <c r="M11" t="s" s="2">
-        <v>140</v>
+        <v>146</v>
       </c>
       <c r="N11" t="s" s="2">
-        <v>141</v>
+        <v>147</v>
       </c>
       <c r="O11" s="2"/>
       <c r="P11" t="s" s="2">
@@ -3708,7 +3701,7 @@
       </c>
       <c r="Q11" s="2"/>
       <c r="R11" t="s" s="2">
-        <v>3</v>
+        <v>79</v>
       </c>
       <c r="S11" t="s" s="2">
         <v>79</v>
@@ -3726,13 +3719,13 @@
         <v>79</v>
       </c>
       <c r="X11" t="s" s="2">
-        <v>79</v>
+        <v>148</v>
       </c>
       <c r="Y11" t="s" s="2">
-        <v>79</v>
+        <v>149</v>
       </c>
       <c r="Z11" t="s" s="2">
-        <v>79</v>
+        <v>150</v>
       </c>
       <c r="AA11" t="s" s="2">
         <v>79</v>
@@ -3750,7 +3743,7 @@
         <v>79</v>
       </c>
       <c r="AF11" t="s" s="2">
-        <v>143</v>
+        <v>151</v>
       </c>
       <c r="AG11" t="s" s="2">
         <v>77</v>
@@ -3762,7 +3755,7 @@
         <v>101</v>
       </c>
       <c r="AJ11" t="s" s="2">
-        <v>125</v>
+        <v>102</v>
       </c>
       <c r="AK11" t="s" s="2">
         <v>79</v>
@@ -3771,10 +3764,10 @@
         <v>79</v>
       </c>
       <c r="AM11" t="s" s="2">
-        <v>79</v>
+        <v>152</v>
       </c>
       <c r="AN11" t="s" s="2">
-        <v>108</v>
+        <v>153</v>
       </c>
       <c r="AO11" t="s" s="2">
         <v>79</v>
@@ -3785,10 +3778,10 @@
     </row>
     <row r="12" hidden="true">
       <c r="A12" t="s" s="2">
-        <v>145</v>
+        <v>154</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>145</v>
+        <v>154</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
@@ -3811,16 +3804,16 @@
         <v>90</v>
       </c>
       <c r="K12" t="s" s="2">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="L12" t="s" s="2">
-        <v>147</v>
+        <v>155</v>
       </c>
       <c r="M12" t="s" s="2">
-        <v>148</v>
+        <v>156</v>
       </c>
       <c r="N12" t="s" s="2">
-        <v>149</v>
+        <v>157</v>
       </c>
       <c r="O12" s="2"/>
       <c r="P12" t="s" s="2">
@@ -3846,13 +3839,13 @@
         <v>79</v>
       </c>
       <c r="X12" t="s" s="2">
-        <v>150</v>
+        <v>158</v>
       </c>
       <c r="Y12" t="s" s="2">
-        <v>151</v>
+        <v>159</v>
       </c>
       <c r="Z12" t="s" s="2">
-        <v>152</v>
+        <v>160</v>
       </c>
       <c r="AA12" t="s" s="2">
         <v>79</v>
@@ -3870,7 +3863,7 @@
         <v>79</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>153</v>
+        <v>161</v>
       </c>
       <c r="AG12" t="s" s="2">
         <v>77</v>
@@ -3882,7 +3875,7 @@
         <v>101</v>
       </c>
       <c r="AJ12" t="s" s="2">
-        <v>125</v>
+        <v>102</v>
       </c>
       <c r="AK12" t="s" s="2">
         <v>79</v>
@@ -3891,10 +3884,10 @@
         <v>79</v>
       </c>
       <c r="AM12" t="s" s="2">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="AN12" t="s" s="2">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="AO12" t="s" s="2">
         <v>79</v>
@@ -3905,10 +3898,10 @@
     </row>
     <row r="13" hidden="true">
       <c r="A13" t="s" s="2">
-        <v>156</v>
+        <v>162</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>156</v>
+        <v>162</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
@@ -3919,28 +3912,28 @@
         <v>77</v>
       </c>
       <c r="G13" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="H13" t="s" s="2">
         <v>79</v>
       </c>
       <c r="I13" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="J13" t="s" s="2">
         <v>90</v>
       </c>
       <c r="K13" t="s" s="2">
-        <v>146</v>
+        <v>133</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>157</v>
+        <v>163</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>158</v>
+        <v>164</v>
       </c>
       <c r="N13" t="s" s="2">
-        <v>159</v>
+        <v>165</v>
       </c>
       <c r="O13" s="2"/>
       <c r="P13" t="s" s="2">
@@ -3966,13 +3959,13 @@
         <v>79</v>
       </c>
       <c r="X13" t="s" s="2">
-        <v>160</v>
+        <v>79</v>
       </c>
       <c r="Y13" t="s" s="2">
-        <v>161</v>
+        <v>79</v>
       </c>
       <c r="Z13" t="s" s="2">
-        <v>162</v>
+        <v>79</v>
       </c>
       <c r="AA13" t="s" s="2">
         <v>79</v>
@@ -3990,19 +3983,19 @@
         <v>79</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH13" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="AI13" t="s" s="2">
         <v>101</v>
       </c>
       <c r="AJ13" t="s" s="2">
-        <v>125</v>
+        <v>102</v>
       </c>
       <c r="AK13" t="s" s="2">
         <v>79</v>
@@ -4011,10 +4004,10 @@
         <v>79</v>
       </c>
       <c r="AM13" t="s" s="2">
-        <v>154</v>
+        <v>79</v>
       </c>
       <c r="AN13" t="s" s="2">
-        <v>155</v>
+        <v>109</v>
       </c>
       <c r="AO13" t="s" s="2">
         <v>79</v>
@@ -4025,10 +4018,10 @@
     </row>
     <row r="14" hidden="true">
       <c r="A14" t="s" s="2">
-        <v>164</v>
+        <v>167</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>164</v>
+        <v>167</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -4045,22 +4038,22 @@
         <v>79</v>
       </c>
       <c r="I14" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="J14" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>133</v>
+        <v>168</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>165</v>
+        <v>169</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>166</v>
+        <v>170</v>
       </c>
       <c r="N14" t="s" s="2">
-        <v>167</v>
+        <v>171</v>
       </c>
       <c r="O14" s="2"/>
       <c r="P14" t="s" s="2">
@@ -4086,13 +4079,13 @@
         <v>79</v>
       </c>
       <c r="X14" t="s" s="2">
-        <v>79</v>
+        <v>172</v>
       </c>
       <c r="Y14" t="s" s="2">
-        <v>79</v>
+        <v>173</v>
       </c>
       <c r="Z14" t="s" s="2">
-        <v>79</v>
+        <v>174</v>
       </c>
       <c r="AA14" t="s" s="2">
         <v>79</v>
@@ -4110,7 +4103,7 @@
         <v>79</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>168</v>
+        <v>175</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>77</v>
@@ -4122,7 +4115,7 @@
         <v>101</v>
       </c>
       <c r="AJ14" t="s" s="2">
-        <v>125</v>
+        <v>102</v>
       </c>
       <c r="AK14" t="s" s="2">
         <v>79</v>
@@ -4134,7 +4127,7 @@
         <v>79</v>
       </c>
       <c r="AN14" t="s" s="2">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="AO14" t="s" s="2">
         <v>79</v>
@@ -4145,14 +4138,14 @@
     </row>
     <row r="15" hidden="true">
       <c r="A15" t="s" s="2">
-        <v>169</v>
+        <v>176</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>169</v>
+        <v>176</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
-        <v>79</v>
+        <v>177</v>
       </c>
       <c r="E15" s="2"/>
       <c r="F15" t="s" s="2">
@@ -4171,16 +4164,16 @@
         <v>79</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>170</v>
+        <v>178</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>171</v>
+        <v>179</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>172</v>
+        <v>180</v>
       </c>
       <c r="N15" t="s" s="2">
-        <v>173</v>
+        <v>181</v>
       </c>
       <c r="O15" s="2"/>
       <c r="P15" t="s" s="2">
@@ -4206,13 +4199,13 @@
         <v>79</v>
       </c>
       <c r="X15" t="s" s="2">
-        <v>174</v>
+        <v>79</v>
       </c>
       <c r="Y15" t="s" s="2">
-        <v>175</v>
+        <v>79</v>
       </c>
       <c r="Z15" t="s" s="2">
-        <v>176</v>
+        <v>79</v>
       </c>
       <c r="AA15" t="s" s="2">
         <v>79</v>
@@ -4230,7 +4223,7 @@
         <v>79</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>177</v>
+        <v>182</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>77</v>
@@ -4242,7 +4235,7 @@
         <v>101</v>
       </c>
       <c r="AJ15" t="s" s="2">
-        <v>125</v>
+        <v>102</v>
       </c>
       <c r="AK15" t="s" s="2">
         <v>79</v>
@@ -4254,7 +4247,7 @@
         <v>79</v>
       </c>
       <c r="AN15" t="s" s="2">
-        <v>108</v>
+        <v>183</v>
       </c>
       <c r="AO15" t="s" s="2">
         <v>79</v>
@@ -4265,21 +4258,21 @@
     </row>
     <row r="16" hidden="true">
       <c r="A16" t="s" s="2">
-        <v>178</v>
+        <v>184</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>178</v>
+        <v>184</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
-        <v>179</v>
+        <v>185</v>
       </c>
       <c r="E16" s="2"/>
       <c r="F16" t="s" s="2">
         <v>77</v>
       </c>
       <c r="G16" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="H16" t="s" s="2">
         <v>79</v>
@@ -4291,16 +4284,16 @@
         <v>79</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>180</v>
+        <v>186</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>181</v>
+        <v>187</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>182</v>
+        <v>188</v>
       </c>
       <c r="N16" t="s" s="2">
-        <v>183</v>
+        <v>189</v>
       </c>
       <c r="O16" s="2"/>
       <c r="P16" t="s" s="2">
@@ -4350,19 +4343,19 @@
         <v>79</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>184</v>
+        <v>190</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH16" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="AI16" t="s" s="2">
-        <v>101</v>
+        <v>79</v>
       </c>
       <c r="AJ16" t="s" s="2">
-        <v>125</v>
+        <v>79</v>
       </c>
       <c r="AK16" t="s" s="2">
         <v>79</v>
@@ -4374,7 +4367,7 @@
         <v>79</v>
       </c>
       <c r="AN16" t="s" s="2">
-        <v>185</v>
+        <v>103</v>
       </c>
       <c r="AO16" t="s" s="2">
         <v>79</v>
@@ -4385,14 +4378,14 @@
     </row>
     <row r="17" hidden="true">
       <c r="A17" t="s" s="2">
-        <v>186</v>
+        <v>191</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>186</v>
+        <v>191</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
-        <v>187</v>
+        <v>111</v>
       </c>
       <c r="E17" s="2"/>
       <c r="F17" t="s" s="2">
@@ -4411,16 +4404,16 @@
         <v>79</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>188</v>
+        <v>112</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>189</v>
+        <v>113</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="N17" t="s" s="2">
-        <v>191</v>
+        <v>115</v>
       </c>
       <c r="O17" s="2"/>
       <c r="P17" t="s" s="2">
@@ -4458,19 +4451,19 @@
         <v>79</v>
       </c>
       <c r="AB17" t="s" s="2">
-        <v>79</v>
+        <v>116</v>
       </c>
       <c r="AC17" t="s" s="2">
-        <v>79</v>
+        <v>117</v>
       </c>
       <c r="AD17" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AE17" t="s" s="2">
-        <v>79</v>
+        <v>118</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>77</v>
@@ -4479,10 +4472,10 @@
         <v>78</v>
       </c>
       <c r="AI17" t="s" s="2">
-        <v>79</v>
+        <v>101</v>
       </c>
       <c r="AJ17" t="s" s="2">
-        <v>79</v>
+        <v>120</v>
       </c>
       <c r="AK17" t="s" s="2">
         <v>79</v>
@@ -4494,7 +4487,7 @@
         <v>79</v>
       </c>
       <c r="AN17" t="s" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="AO17" t="s" s="2">
         <v>79</v>
@@ -4505,21 +4498,23 @@
     </row>
     <row r="18" hidden="true">
       <c r="A18" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>193</v>
-      </c>
-      <c r="C18" s="2"/>
+        <v>191</v>
+      </c>
+      <c r="C18" t="s" s="2">
+        <v>195</v>
+      </c>
       <c r="D18" t="s" s="2">
-        <v>110</v>
+        <v>79</v>
       </c>
       <c r="E18" s="2"/>
       <c r="F18" t="s" s="2">
         <v>77</v>
       </c>
       <c r="G18" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="H18" t="s" s="2">
         <v>79</v>
@@ -4531,17 +4526,15 @@
         <v>79</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>111</v>
+        <v>196</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>112</v>
+        <v>197</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>194</v>
-      </c>
-      <c r="N18" t="s" s="2">
-        <v>114</v>
-      </c>
+        <v>198</v>
+      </c>
+      <c r="N18" s="2"/>
       <c r="O18" s="2"/>
       <c r="P18" t="s" s="2">
         <v>79</v>
@@ -4578,19 +4571,19 @@
         <v>79</v>
       </c>
       <c r="AB18" t="s" s="2">
-        <v>115</v>
+        <v>79</v>
       </c>
       <c r="AC18" t="s" s="2">
-        <v>116</v>
+        <v>79</v>
       </c>
       <c r="AD18" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AE18" t="s" s="2">
-        <v>117</v>
+        <v>79</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>77</v>
@@ -4602,7 +4595,7 @@
         <v>101</v>
       </c>
       <c r="AJ18" t="s" s="2">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="AK18" t="s" s="2">
         <v>79</v>
@@ -4614,7 +4607,7 @@
         <v>79</v>
       </c>
       <c r="AN18" t="s" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="AO18" t="s" s="2">
         <v>79</v>
@@ -4625,13 +4618,13 @@
     </row>
     <row r="19" hidden="true">
       <c r="A19" t="s" s="2">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="C19" t="s" s="2">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="D19" t="s" s="2">
         <v>79</v>
@@ -4653,13 +4646,13 @@
         <v>79</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="N19" s="2"/>
       <c r="O19" s="2"/>
@@ -4710,7 +4703,7 @@
         <v>79</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>77</v>
@@ -4722,7 +4715,7 @@
         <v>101</v>
       </c>
       <c r="AJ19" t="s" s="2">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="AK19" t="s" s="2">
         <v>79</v>
@@ -4734,7 +4727,7 @@
         <v>79</v>
       </c>
       <c r="AN19" t="s" s="2">
-        <v>102</v>
+        <v>79</v>
       </c>
       <c r="AO19" t="s" s="2">
         <v>79</v>
@@ -4745,44 +4738,46 @@
     </row>
     <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>193</v>
-      </c>
-      <c r="C20" t="s" s="2">
-        <v>202</v>
-      </c>
+        <v>204</v>
+      </c>
+      <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
-        <v>79</v>
+        <v>111</v>
       </c>
       <c r="E20" s="2"/>
       <c r="F20" t="s" s="2">
         <v>77</v>
       </c>
       <c r="G20" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="H20" t="s" s="2">
         <v>79</v>
       </c>
       <c r="I20" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="J20" t="s" s="2">
         <v>79</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>203</v>
+        <v>112</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>205</v>
-      </c>
-      <c r="N20" s="2"/>
-      <c r="O20" s="2"/>
+        <v>206</v>
+      </c>
+      <c r="N20" t="s" s="2">
+        <v>115</v>
+      </c>
+      <c r="O20" t="s" s="2">
+        <v>207</v>
+      </c>
       <c r="P20" t="s" s="2">
         <v>79</v>
       </c>
@@ -4818,19 +4813,19 @@
         <v>79</v>
       </c>
       <c r="AB20" t="s" s="2">
-        <v>79</v>
+        <v>116</v>
       </c>
       <c r="AC20" t="s" s="2">
-        <v>79</v>
+        <v>117</v>
       </c>
       <c r="AD20" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AE20" t="s" s="2">
-        <v>79</v>
+        <v>118</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>195</v>
+        <v>208</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>77</v>
@@ -4842,7 +4837,7 @@
         <v>101</v>
       </c>
       <c r="AJ20" t="s" s="2">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="AK20" t="s" s="2">
         <v>79</v>
@@ -4854,7 +4849,7 @@
         <v>79</v>
       </c>
       <c r="AN20" t="s" s="2">
-        <v>79</v>
+        <v>103</v>
       </c>
       <c r="AO20" t="s" s="2">
         <v>79</v>
@@ -4865,14 +4860,14 @@
     </row>
     <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
-        <v>110</v>
+        <v>79</v>
       </c>
       <c r="E21" s="2"/>
       <c r="F21" t="s" s="2">
@@ -4885,25 +4880,23 @@
         <v>79</v>
       </c>
       <c r="I21" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="J21" t="s" s="2">
         <v>90</v>
       </c>
-      <c r="J21" t="s" s="2">
-        <v>79</v>
-      </c>
       <c r="K21" t="s" s="2">
-        <v>111</v>
+        <v>210</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>207</v>
+        <v>211</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>208</v>
-      </c>
-      <c r="N21" t="s" s="2">
-        <v>114</v>
-      </c>
+        <v>212</v>
+      </c>
+      <c r="N21" s="2"/>
       <c r="O21" t="s" s="2">
-        <v>209</v>
+        <v>213</v>
       </c>
       <c r="P21" t="s" s="2">
         <v>79</v>
@@ -4940,19 +4933,19 @@
         <v>79</v>
       </c>
       <c r="AB21" t="s" s="2">
-        <v>115</v>
+        <v>79</v>
       </c>
       <c r="AC21" t="s" s="2">
-        <v>116</v>
+        <v>79</v>
       </c>
       <c r="AD21" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AE21" t="s" s="2">
-        <v>117</v>
+        <v>79</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>77</v>
@@ -4964,22 +4957,22 @@
         <v>101</v>
       </c>
       <c r="AJ21" t="s" s="2">
-        <v>119</v>
+        <v>102</v>
       </c>
       <c r="AK21" t="s" s="2">
-        <v>79</v>
+        <v>214</v>
       </c>
       <c r="AL21" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AM21" t="s" s="2">
-        <v>79</v>
+        <v>215</v>
       </c>
       <c r="AN21" t="s" s="2">
-        <v>102</v>
+        <v>216</v>
       </c>
       <c r="AO21" t="s" s="2">
-        <v>79</v>
+        <v>217</v>
       </c>
       <c r="AP21" t="s" s="2">
         <v>79</v>
@@ -4987,14 +4980,14 @@
     </row>
     <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>211</v>
+        <v>218</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>211</v>
+        <v>218</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
-        <v>79</v>
+        <v>219</v>
       </c>
       <c r="E22" s="2"/>
       <c r="F22" t="s" s="2">
@@ -5013,17 +5006,19 @@
         <v>90</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>212</v>
+        <v>220</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>213</v>
+        <v>221</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>214</v>
-      </c>
-      <c r="N22" s="2"/>
+        <v>222</v>
+      </c>
+      <c r="N22" t="s" s="2">
+        <v>223</v>
+      </c>
       <c r="O22" t="s" s="2">
-        <v>215</v>
+        <v>224</v>
       </c>
       <c r="P22" t="s" s="2">
         <v>79</v>
@@ -5072,7 +5067,7 @@
         <v>79</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>211</v>
+        <v>218</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>77</v>
@@ -5084,22 +5079,22 @@
         <v>101</v>
       </c>
       <c r="AJ22" t="s" s="2">
-        <v>125</v>
+        <v>225</v>
       </c>
       <c r="AK22" t="s" s="2">
-        <v>216</v>
+        <v>226</v>
       </c>
       <c r="AL22" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AM22" t="s" s="2">
-        <v>217</v>
+        <v>227</v>
       </c>
       <c r="AN22" t="s" s="2">
-        <v>218</v>
+        <v>228</v>
       </c>
       <c r="AO22" t="s" s="2">
-        <v>219</v>
+        <v>79</v>
       </c>
       <c r="AP22" t="s" s="2">
         <v>79</v>
@@ -5107,14 +5102,14 @@
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>220</v>
+        <v>229</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>220</v>
+        <v>229</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
-        <v>221</v>
+        <v>230</v>
       </c>
       <c r="E23" s="2"/>
       <c r="F23" t="s" s="2">
@@ -5133,20 +5128,18 @@
         <v>90</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>222</v>
+        <v>231</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>223</v>
+        <v>232</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>224</v>
+        <v>233</v>
       </c>
       <c r="N23" t="s" s="2">
-        <v>225</v>
-      </c>
-      <c r="O23" t="s" s="2">
-        <v>226</v>
-      </c>
+        <v>234</v>
+      </c>
+      <c r="O23" s="2"/>
       <c r="P23" t="s" s="2">
         <v>79</v>
       </c>
@@ -5194,7 +5187,7 @@
         <v>79</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>220</v>
+        <v>229</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>77</v>
@@ -5206,19 +5199,19 @@
         <v>101</v>
       </c>
       <c r="AJ23" t="s" s="2">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="AK23" t="s" s="2">
-        <v>228</v>
+        <v>235</v>
       </c>
       <c r="AL23" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AM23" t="s" s="2">
-        <v>229</v>
+        <v>236</v>
       </c>
       <c r="AN23" t="s" s="2">
-        <v>230</v>
+        <v>237</v>
       </c>
       <c r="AO23" t="s" s="2">
         <v>79</v>
@@ -5229,44 +5222,46 @@
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>231</v>
+        <v>238</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>231</v>
+        <v>238</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
-        <v>232</v>
+        <v>79</v>
       </c>
       <c r="E24" s="2"/>
       <c r="F24" t="s" s="2">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="G24" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="H24" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="I24" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="J24" t="s" s="2">
         <v>90</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>233</v>
+        <v>168</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>234</v>
+        <v>239</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>235</v>
+        <v>240</v>
       </c>
       <c r="N24" t="s" s="2">
-        <v>236</v>
-      </c>
-      <c r="O24" s="2"/>
+        <v>241</v>
+      </c>
+      <c r="O24" t="s" s="2">
+        <v>242</v>
+      </c>
       <c r="P24" t="s" s="2">
         <v>79</v>
       </c>
@@ -5290,13 +5285,13 @@
         <v>79</v>
       </c>
       <c r="X24" t="s" s="2">
-        <v>79</v>
+        <v>243</v>
       </c>
       <c r="Y24" t="s" s="2">
-        <v>79</v>
+        <v>244</v>
       </c>
       <c r="Z24" t="s" s="2">
-        <v>79</v>
+        <v>245</v>
       </c>
       <c r="AA24" t="s" s="2">
         <v>79</v>
@@ -5314,34 +5309,34 @@
         <v>79</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>231</v>
+        <v>238</v>
       </c>
       <c r="AG24" t="s" s="2">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="AH24" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="AI24" t="s" s="2">
         <v>101</v>
       </c>
       <c r="AJ24" t="s" s="2">
-        <v>227</v>
+        <v>102</v>
       </c>
       <c r="AK24" t="s" s="2">
-        <v>237</v>
+        <v>246</v>
       </c>
       <c r="AL24" t="s" s="2">
-        <v>79</v>
+        <v>247</v>
       </c>
       <c r="AM24" t="s" s="2">
-        <v>238</v>
+        <v>248</v>
       </c>
       <c r="AN24" t="s" s="2">
-        <v>239</v>
+        <v>249</v>
       </c>
       <c r="AO24" t="s" s="2">
-        <v>79</v>
+        <v>250</v>
       </c>
       <c r="AP24" t="s" s="2">
         <v>79</v>
@@ -5349,10 +5344,10 @@
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>240</v>
+        <v>251</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>240</v>
+        <v>251</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -5363,31 +5358,31 @@
         <v>89</v>
       </c>
       <c r="G25" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="H25" t="s" s="2">
         <v>90</v>
       </c>
       <c r="I25" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="J25" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>170</v>
+        <v>252</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>241</v>
+        <v>253</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>242</v>
+        <v>254</v>
       </c>
       <c r="N25" t="s" s="2">
-        <v>243</v>
+        <v>255</v>
       </c>
       <c r="O25" t="s" s="2">
-        <v>244</v>
+        <v>256</v>
       </c>
       <c r="P25" t="s" s="2">
         <v>79</v>
@@ -5412,58 +5407,56 @@
         <v>79</v>
       </c>
       <c r="X25" t="s" s="2">
-        <v>245</v>
+        <v>172</v>
       </c>
       <c r="Y25" t="s" s="2">
-        <v>246</v>
+        <v>257</v>
       </c>
       <c r="Z25" t="s" s="2">
-        <v>247</v>
+        <v>258</v>
       </c>
       <c r="AA25" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AB25" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC25" t="s" s="2">
-        <v>79</v>
-      </c>
+        <v>259</v>
+      </c>
+      <c r="AC25" s="2"/>
       <c r="AD25" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AE25" t="s" s="2">
-        <v>79</v>
+        <v>118</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>240</v>
+        <v>251</v>
       </c>
       <c r="AG25" t="s" s="2">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="AH25" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="AI25" t="s" s="2">
         <v>101</v>
       </c>
       <c r="AJ25" t="s" s="2">
-        <v>125</v>
+        <v>102</v>
       </c>
       <c r="AK25" t="s" s="2">
-        <v>248</v>
+        <v>79</v>
       </c>
       <c r="AL25" t="s" s="2">
-        <v>249</v>
+        <v>79</v>
       </c>
       <c r="AM25" t="s" s="2">
-        <v>250</v>
+        <v>260</v>
       </c>
       <c r="AN25" t="s" s="2">
-        <v>251</v>
+        <v>261</v>
       </c>
       <c r="AO25" t="s" s="2">
-        <v>252</v>
+        <v>262</v>
       </c>
       <c r="AP25" t="s" s="2">
         <v>79</v>
@@ -5471,12 +5464,14 @@
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>253</v>
+        <v>263</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>253</v>
-      </c>
-      <c r="C26" s="2"/>
+        <v>251</v>
+      </c>
+      <c r="C26" t="s" s="2">
+        <v>264</v>
+      </c>
       <c r="D26" t="s" s="2">
         <v>79</v>
       </c>
@@ -5485,7 +5480,7 @@
         <v>89</v>
       </c>
       <c r="G26" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="H26" t="s" s="2">
         <v>90</v>
@@ -5497,19 +5492,19 @@
         <v>79</v>
       </c>
       <c r="K26" t="s" s="2">
+        <v>252</v>
+      </c>
+      <c r="L26" t="s" s="2">
+        <v>253</v>
+      </c>
+      <c r="M26" t="s" s="2">
         <v>254</v>
       </c>
-      <c r="L26" t="s" s="2">
+      <c r="N26" t="s" s="2">
         <v>255</v>
       </c>
-      <c r="M26" t="s" s="2">
+      <c r="O26" t="s" s="2">
         <v>256</v>
-      </c>
-      <c r="N26" t="s" s="2">
-        <v>257</v>
-      </c>
-      <c r="O26" t="s" s="2">
-        <v>258</v>
       </c>
       <c r="P26" t="s" s="2">
         <v>79</v>
@@ -5534,29 +5529,31 @@
         <v>79</v>
       </c>
       <c r="X26" t="s" s="2">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="Y26" t="s" s="2">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="Z26" t="s" s="2">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="AA26" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AB26" t="s" s="2">
-        <v>261</v>
-      </c>
-      <c r="AC26" s="2"/>
+        <v>79</v>
+      </c>
+      <c r="AC26" t="s" s="2">
+        <v>79</v>
+      </c>
       <c r="AD26" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AE26" t="s" s="2">
-        <v>117</v>
+        <v>79</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>77</v>
@@ -5568,7 +5565,7 @@
         <v>101</v>
       </c>
       <c r="AJ26" t="s" s="2">
-        <v>125</v>
+        <v>102</v>
       </c>
       <c r="AK26" t="s" s="2">
         <v>79</v>
@@ -5577,13 +5574,13 @@
         <v>79</v>
       </c>
       <c r="AM26" t="s" s="2">
+        <v>260</v>
+      </c>
+      <c r="AN26" t="s" s="2">
+        <v>261</v>
+      </c>
+      <c r="AO26" t="s" s="2">
         <v>262</v>
-      </c>
-      <c r="AN26" t="s" s="2">
-        <v>263</v>
-      </c>
-      <c r="AO26" t="s" s="2">
-        <v>264</v>
       </c>
       <c r="AP26" t="s" s="2">
         <v>79</v>
@@ -5594,23 +5591,21 @@
         <v>265</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>253</v>
-      </c>
-      <c r="C27" t="s" s="2">
         <v>266</v>
       </c>
+      <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
         <v>79</v>
       </c>
       <c r="E27" s="2"/>
       <c r="F27" t="s" s="2">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="G27" t="s" s="2">
         <v>89</v>
       </c>
       <c r="H27" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="I27" t="s" s="2">
         <v>79</v>
@@ -5619,20 +5614,16 @@
         <v>79</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>254</v>
+        <v>105</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>255</v>
+        <v>106</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>256</v>
-      </c>
-      <c r="N27" t="s" s="2">
-        <v>257</v>
-      </c>
-      <c r="O27" t="s" s="2">
-        <v>258</v>
-      </c>
+        <v>107</v>
+      </c>
+      <c r="N27" s="2"/>
+      <c r="O27" s="2"/>
       <c r="P27" t="s" s="2">
         <v>79</v>
       </c>
@@ -5656,13 +5647,13 @@
         <v>79</v>
       </c>
       <c r="X27" t="s" s="2">
-        <v>174</v>
+        <v>79</v>
       </c>
       <c r="Y27" t="s" s="2">
-        <v>259</v>
+        <v>79</v>
       </c>
       <c r="Z27" t="s" s="2">
-        <v>260</v>
+        <v>79</v>
       </c>
       <c r="AA27" t="s" s="2">
         <v>79</v>
@@ -5680,19 +5671,19 @@
         <v>79</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>253</v>
+        <v>108</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH27" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="AI27" t="s" s="2">
-        <v>101</v>
+        <v>79</v>
       </c>
       <c r="AJ27" t="s" s="2">
-        <v>125</v>
+        <v>79</v>
       </c>
       <c r="AK27" t="s" s="2">
         <v>79</v>
@@ -5701,13 +5692,13 @@
         <v>79</v>
       </c>
       <c r="AM27" t="s" s="2">
-        <v>262</v>
+        <v>79</v>
       </c>
       <c r="AN27" t="s" s="2">
-        <v>263</v>
+        <v>109</v>
       </c>
       <c r="AO27" t="s" s="2">
-        <v>264</v>
+        <v>79</v>
       </c>
       <c r="AP27" t="s" s="2">
         <v>79</v>
@@ -5722,14 +5713,14 @@
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
-        <v>79</v>
+        <v>111</v>
       </c>
       <c r="E28" s="2"/>
       <c r="F28" t="s" s="2">
         <v>77</v>
       </c>
       <c r="G28" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="H28" t="s" s="2">
         <v>79</v>
@@ -5741,15 +5732,17 @@
         <v>79</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>104</v>
+        <v>112</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>105</v>
+        <v>113</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>106</v>
-      </c>
-      <c r="N28" s="2"/>
+        <v>114</v>
+      </c>
+      <c r="N28" t="s" s="2">
+        <v>115</v>
+      </c>
       <c r="O28" s="2"/>
       <c r="P28" t="s" s="2">
         <v>79</v>
@@ -5786,31 +5779,31 @@
         <v>79</v>
       </c>
       <c r="AB28" t="s" s="2">
-        <v>79</v>
+        <v>116</v>
       </c>
       <c r="AC28" t="s" s="2">
-        <v>79</v>
+        <v>117</v>
       </c>
       <c r="AD28" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AE28" t="s" s="2">
-        <v>79</v>
+        <v>118</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>107</v>
+        <v>119</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH28" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="AI28" t="s" s="2">
-        <v>79</v>
+        <v>101</v>
       </c>
       <c r="AJ28" t="s" s="2">
-        <v>79</v>
+        <v>120</v>
       </c>
       <c r="AK28" t="s" s="2">
         <v>79</v>
@@ -5822,7 +5815,7 @@
         <v>79</v>
       </c>
       <c r="AN28" t="s" s="2">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="AO28" t="s" s="2">
         <v>79</v>
@@ -5840,37 +5833,39 @@
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
-        <v>110</v>
+        <v>79</v>
       </c>
       <c r="E29" s="2"/>
       <c r="F29" t="s" s="2">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="G29" t="s" s="2">
         <v>78</v>
       </c>
       <c r="H29" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="I29" t="s" s="2">
         <v>79</v>
       </c>
       <c r="J29" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>111</v>
+        <v>144</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>112</v>
+        <v>271</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>113</v>
+        <v>272</v>
       </c>
       <c r="N29" t="s" s="2">
-        <v>114</v>
-      </c>
-      <c r="O29" s="2"/>
+        <v>273</v>
+      </c>
+      <c r="O29" t="s" s="2">
+        <v>274</v>
+      </c>
       <c r="P29" t="s" s="2">
         <v>79</v>
       </c>
@@ -5906,19 +5901,19 @@
         <v>79</v>
       </c>
       <c r="AB29" t="s" s="2">
-        <v>115</v>
+        <v>79</v>
       </c>
       <c r="AC29" t="s" s="2">
-        <v>116</v>
+        <v>79</v>
       </c>
       <c r="AD29" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AE29" t="s" s="2">
-        <v>117</v>
+        <v>79</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>118</v>
+        <v>275</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>77</v>
@@ -5930,7 +5925,7 @@
         <v>101</v>
       </c>
       <c r="AJ29" t="s" s="2">
-        <v>119</v>
+        <v>102</v>
       </c>
       <c r="AK29" t="s" s="2">
         <v>79</v>
@@ -5939,10 +5934,10 @@
         <v>79</v>
       </c>
       <c r="AM29" t="s" s="2">
-        <v>79</v>
+        <v>276</v>
       </c>
       <c r="AN29" t="s" s="2">
-        <v>102</v>
+        <v>277</v>
       </c>
       <c r="AO29" t="s" s="2">
         <v>79</v>
@@ -5953,10 +5948,10 @@
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>271</v>
+        <v>278</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>272</v>
+        <v>279</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -5964,35 +5959,31 @@
       </c>
       <c r="E30" s="2"/>
       <c r="F30" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="G30" t="s" s="2">
         <v>89</v>
       </c>
-      <c r="G30" t="s" s="2">
-        <v>78</v>
-      </c>
       <c r="H30" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="I30" t="s" s="2">
         <v>79</v>
       </c>
       <c r="J30" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>146</v>
+        <v>105</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>273</v>
+        <v>106</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>274</v>
-      </c>
-      <c r="N30" t="s" s="2">
-        <v>275</v>
-      </c>
-      <c r="O30" t="s" s="2">
-        <v>276</v>
-      </c>
+        <v>107</v>
+      </c>
+      <c r="N30" s="2"/>
+      <c r="O30" s="2"/>
       <c r="P30" t="s" s="2">
         <v>79</v>
       </c>
@@ -6040,19 +6031,19 @@
         <v>79</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>277</v>
+        <v>108</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH30" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="AI30" t="s" s="2">
-        <v>101</v>
+        <v>79</v>
       </c>
       <c r="AJ30" t="s" s="2">
-        <v>125</v>
+        <v>79</v>
       </c>
       <c r="AK30" t="s" s="2">
         <v>79</v>
@@ -6061,10 +6052,10 @@
         <v>79</v>
       </c>
       <c r="AM30" t="s" s="2">
-        <v>278</v>
+        <v>79</v>
       </c>
       <c r="AN30" t="s" s="2">
-        <v>279</v>
+        <v>109</v>
       </c>
       <c r="AO30" t="s" s="2">
         <v>79</v>
@@ -6082,14 +6073,14 @@
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
-        <v>79</v>
+        <v>111</v>
       </c>
       <c r="E31" s="2"/>
       <c r="F31" t="s" s="2">
         <v>77</v>
       </c>
       <c r="G31" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="H31" t="s" s="2">
         <v>79</v>
@@ -6101,15 +6092,17 @@
         <v>79</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>104</v>
+        <v>112</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>105</v>
+        <v>113</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>106</v>
-      </c>
-      <c r="N31" s="2"/>
+        <v>114</v>
+      </c>
+      <c r="N31" t="s" s="2">
+        <v>115</v>
+      </c>
       <c r="O31" s="2"/>
       <c r="P31" t="s" s="2">
         <v>79</v>
@@ -6146,31 +6139,31 @@
         <v>79</v>
       </c>
       <c r="AB31" t="s" s="2">
-        <v>79</v>
+        <v>116</v>
       </c>
       <c r="AC31" t="s" s="2">
-        <v>79</v>
+        <v>117</v>
       </c>
       <c r="AD31" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AE31" t="s" s="2">
-        <v>79</v>
+        <v>118</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>107</v>
+        <v>119</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH31" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="AI31" t="s" s="2">
-        <v>79</v>
+        <v>101</v>
       </c>
       <c r="AJ31" t="s" s="2">
-        <v>79</v>
+        <v>120</v>
       </c>
       <c r="AK31" t="s" s="2">
         <v>79</v>
@@ -6182,7 +6175,7 @@
         <v>79</v>
       </c>
       <c r="AN31" t="s" s="2">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="AO31" t="s" s="2">
         <v>79</v>
@@ -6200,43 +6193,45 @@
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
-        <v>110</v>
+        <v>79</v>
       </c>
       <c r="E32" s="2"/>
       <c r="F32" t="s" s="2">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="G32" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="H32" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="I32" t="s" s="2">
         <v>79</v>
       </c>
       <c r="J32" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>111</v>
+        <v>133</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>112</v>
+        <v>284</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>113</v>
+        <v>285</v>
       </c>
       <c r="N32" t="s" s="2">
-        <v>114</v>
-      </c>
-      <c r="O32" s="2"/>
+        <v>286</v>
+      </c>
+      <c r="O32" t="s" s="2">
+        <v>287</v>
+      </c>
       <c r="P32" t="s" s="2">
         <v>79</v>
       </c>
       <c r="Q32" s="2"/>
       <c r="R32" t="s" s="2">
-        <v>79</v>
+        <v>288</v>
       </c>
       <c r="S32" t="s" s="2">
         <v>79</v>
@@ -6266,31 +6261,31 @@
         <v>79</v>
       </c>
       <c r="AB32" t="s" s="2">
-        <v>115</v>
+        <v>79</v>
       </c>
       <c r="AC32" t="s" s="2">
-        <v>116</v>
+        <v>79</v>
       </c>
       <c r="AD32" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AE32" t="s" s="2">
-        <v>117</v>
+        <v>79</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>118</v>
+        <v>289</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH32" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="AI32" t="s" s="2">
         <v>101</v>
       </c>
       <c r="AJ32" t="s" s="2">
-        <v>119</v>
+        <v>102</v>
       </c>
       <c r="AK32" t="s" s="2">
         <v>79</v>
@@ -6299,10 +6294,10 @@
         <v>79</v>
       </c>
       <c r="AM32" t="s" s="2">
-        <v>79</v>
+        <v>290</v>
       </c>
       <c r="AN32" t="s" s="2">
-        <v>102</v>
+        <v>291</v>
       </c>
       <c r="AO32" t="s" s="2">
         <v>79</v>
@@ -6313,10 +6308,10 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>284</v>
+        <v>292</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>285</v>
+        <v>293</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -6324,13 +6319,13 @@
       </c>
       <c r="E33" s="2"/>
       <c r="F33" t="s" s="2">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="G33" t="s" s="2">
         <v>89</v>
       </c>
       <c r="H33" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="I33" t="s" s="2">
         <v>79</v>
@@ -6339,26 +6334,24 @@
         <v>90</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>133</v>
+        <v>105</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>286</v>
+        <v>294</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>287</v>
+        <v>295</v>
       </c>
       <c r="N33" t="s" s="2">
-        <v>288</v>
-      </c>
-      <c r="O33" t="s" s="2">
-        <v>289</v>
-      </c>
+        <v>296</v>
+      </c>
+      <c r="O33" s="2"/>
       <c r="P33" t="s" s="2">
         <v>79</v>
       </c>
       <c r="Q33" s="2"/>
       <c r="R33" t="s" s="2">
-        <v>290</v>
+        <v>79</v>
       </c>
       <c r="S33" t="s" s="2">
         <v>79</v>
@@ -6400,7 +6393,7 @@
         <v>79</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>291</v>
+        <v>297</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>77</v>
@@ -6412,7 +6405,7 @@
         <v>101</v>
       </c>
       <c r="AJ33" t="s" s="2">
-        <v>125</v>
+        <v>102</v>
       </c>
       <c r="AK33" t="s" s="2">
         <v>79</v>
@@ -6421,10 +6414,10 @@
         <v>79</v>
       </c>
       <c r="AM33" t="s" s="2">
-        <v>292</v>
+        <v>298</v>
       </c>
       <c r="AN33" t="s" s="2">
-        <v>293</v>
+        <v>299</v>
       </c>
       <c r="AO33" t="s" s="2">
         <v>79</v>
@@ -6435,10 +6428,10 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>294</v>
+        <v>300</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>295</v>
+        <v>301</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -6446,13 +6439,13 @@
       </c>
       <c r="E34" s="2"/>
       <c r="F34" t="s" s="2">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="G34" t="s" s="2">
         <v>89</v>
       </c>
       <c r="H34" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="I34" t="s" s="2">
         <v>79</v>
@@ -6461,24 +6454,26 @@
         <v>90</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>104</v>
+        <v>168</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>296</v>
+        <v>302</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>297</v>
+        <v>303</v>
       </c>
       <c r="N34" t="s" s="2">
-        <v>298</v>
-      </c>
-      <c r="O34" s="2"/>
+        <v>304</v>
+      </c>
+      <c r="O34" t="s" s="2">
+        <v>305</v>
+      </c>
       <c r="P34" t="s" s="2">
         <v>79</v>
       </c>
       <c r="Q34" s="2"/>
       <c r="R34" t="s" s="2">
-        <v>79</v>
+        <v>306</v>
       </c>
       <c r="S34" t="s" s="2">
         <v>79</v>
@@ -6520,7 +6515,7 @@
         <v>79</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>299</v>
+        <v>307</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>77</v>
@@ -6532,7 +6527,7 @@
         <v>101</v>
       </c>
       <c r="AJ34" t="s" s="2">
-        <v>125</v>
+        <v>102</v>
       </c>
       <c r="AK34" t="s" s="2">
         <v>79</v>
@@ -6541,10 +6536,10 @@
         <v>79</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>300</v>
+        <v>308</v>
       </c>
       <c r="AN34" t="s" s="2">
-        <v>301</v>
+        <v>309</v>
       </c>
       <c r="AO34" t="s" s="2">
         <v>79</v>
@@ -6555,10 +6550,10 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>302</v>
+        <v>310</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>303</v>
+        <v>311</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -6566,13 +6561,13 @@
       </c>
       <c r="E35" s="2"/>
       <c r="F35" t="s" s="2">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="G35" t="s" s="2">
         <v>89</v>
       </c>
       <c r="H35" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="I35" t="s" s="2">
         <v>79</v>
@@ -6581,29 +6576,29 @@
         <v>90</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>170</v>
+        <v>105</v>
       </c>
       <c r="L35" t="s" s="2">
+        <v>312</v>
+      </c>
+      <c r="M35" t="s" s="2">
+        <v>313</v>
+      </c>
+      <c r="N35" t="s" s="2">
         <v>304</v>
       </c>
-      <c r="M35" t="s" s="2">
-        <v>305</v>
-      </c>
-      <c r="N35" t="s" s="2">
-        <v>306</v>
-      </c>
       <c r="O35" t="s" s="2">
-        <v>307</v>
+        <v>314</v>
       </c>
       <c r="P35" t="s" s="2">
         <v>79</v>
       </c>
       <c r="Q35" s="2"/>
       <c r="R35" t="s" s="2">
-        <v>308</v>
+        <v>79</v>
       </c>
       <c r="S35" t="s" s="2">
-        <v>79</v>
+        <v>315</v>
       </c>
       <c r="T35" t="s" s="2">
         <v>79</v>
@@ -6642,7 +6637,7 @@
         <v>79</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>309</v>
+        <v>316</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>77</v>
@@ -6654,7 +6649,7 @@
         <v>101</v>
       </c>
       <c r="AJ35" t="s" s="2">
-        <v>125</v>
+        <v>102</v>
       </c>
       <c r="AK35" t="s" s="2">
         <v>79</v>
@@ -6663,10 +6658,10 @@
         <v>79</v>
       </c>
       <c r="AM35" t="s" s="2">
-        <v>310</v>
+        <v>317</v>
       </c>
       <c r="AN35" t="s" s="2">
-        <v>311</v>
+        <v>318</v>
       </c>
       <c r="AO35" t="s" s="2">
         <v>79</v>
@@ -6677,10 +6672,10 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>312</v>
+        <v>319</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>313</v>
+        <v>320</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -6703,19 +6698,19 @@
         <v>90</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>104</v>
+        <v>321</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>314</v>
+        <v>322</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>315</v>
+        <v>323</v>
       </c>
       <c r="N36" t="s" s="2">
-        <v>306</v>
+        <v>324</v>
       </c>
       <c r="O36" t="s" s="2">
-        <v>316</v>
+        <v>325</v>
       </c>
       <c r="P36" t="s" s="2">
         <v>79</v>
@@ -6725,7 +6720,7 @@
         <v>79</v>
       </c>
       <c r="S36" t="s" s="2">
-        <v>317</v>
+        <v>79</v>
       </c>
       <c r="T36" t="s" s="2">
         <v>79</v>
@@ -6764,7 +6759,7 @@
         <v>79</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>318</v>
+        <v>326</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>77</v>
@@ -6776,7 +6771,7 @@
         <v>101</v>
       </c>
       <c r="AJ36" t="s" s="2">
-        <v>125</v>
+        <v>102</v>
       </c>
       <c r="AK36" t="s" s="2">
         <v>79</v>
@@ -6785,10 +6780,10 @@
         <v>79</v>
       </c>
       <c r="AM36" t="s" s="2">
-        <v>319</v>
+        <v>327</v>
       </c>
       <c r="AN36" t="s" s="2">
-        <v>320</v>
+        <v>328</v>
       </c>
       <c r="AO36" t="s" s="2">
         <v>79</v>
@@ -6799,10 +6794,10 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>321</v>
+        <v>329</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>322</v>
+        <v>330</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6825,19 +6820,19 @@
         <v>90</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>323</v>
+        <v>105</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>324</v>
+        <v>331</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>325</v>
+        <v>332</v>
       </c>
       <c r="N37" t="s" s="2">
-        <v>326</v>
+        <v>333</v>
       </c>
       <c r="O37" t="s" s="2">
-        <v>327</v>
+        <v>334</v>
       </c>
       <c r="P37" t="s" s="2">
         <v>79</v>
@@ -6886,7 +6881,7 @@
         <v>79</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>328</v>
+        <v>335</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>77</v>
@@ -6898,7 +6893,7 @@
         <v>101</v>
       </c>
       <c r="AJ37" t="s" s="2">
-        <v>125</v>
+        <v>102</v>
       </c>
       <c r="AK37" t="s" s="2">
         <v>79</v>
@@ -6907,10 +6902,10 @@
         <v>79</v>
       </c>
       <c r="AM37" t="s" s="2">
-        <v>329</v>
+        <v>336</v>
       </c>
       <c r="AN37" t="s" s="2">
-        <v>330</v>
+        <v>337</v>
       </c>
       <c r="AO37" t="s" s="2">
         <v>79</v>
@@ -6921,24 +6916,24 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>331</v>
+        <v>338</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>332</v>
+        <v>338</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
-        <v>79</v>
+        <v>339</v>
       </c>
       <c r="E38" s="2"/>
       <c r="F38" t="s" s="2">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="G38" t="s" s="2">
         <v>89</v>
       </c>
       <c r="H38" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="I38" t="s" s="2">
         <v>79</v>
@@ -6947,19 +6942,19 @@
         <v>90</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>104</v>
+        <v>252</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>333</v>
+        <v>340</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>334</v>
+        <v>341</v>
       </c>
       <c r="N38" t="s" s="2">
-        <v>335</v>
+        <v>342</v>
       </c>
       <c r="O38" t="s" s="2">
-        <v>336</v>
+        <v>343</v>
       </c>
       <c r="P38" t="s" s="2">
         <v>79</v>
@@ -6969,7 +6964,7 @@
         <v>79</v>
       </c>
       <c r="S38" t="s" s="2">
-        <v>79</v>
+        <v>344</v>
       </c>
       <c r="T38" t="s" s="2">
         <v>79</v>
@@ -6984,13 +6979,13 @@
         <v>79</v>
       </c>
       <c r="X38" t="s" s="2">
-        <v>79</v>
+        <v>148</v>
       </c>
       <c r="Y38" t="s" s="2">
-        <v>79</v>
+        <v>345</v>
       </c>
       <c r="Z38" t="s" s="2">
-        <v>79</v>
+        <v>346</v>
       </c>
       <c r="AA38" t="s" s="2">
         <v>79</v>
@@ -7008,10 +7003,10 @@
         <v>79</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="AG38" t="s" s="2">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="AH38" t="s" s="2">
         <v>89</v>
@@ -7020,37 +7015,37 @@
         <v>101</v>
       </c>
       <c r="AJ38" t="s" s="2">
-        <v>125</v>
+        <v>102</v>
       </c>
       <c r="AK38" t="s" s="2">
-        <v>79</v>
+        <v>347</v>
       </c>
       <c r="AL38" t="s" s="2">
-        <v>79</v>
+        <v>348</v>
       </c>
       <c r="AM38" t="s" s="2">
-        <v>338</v>
+        <v>349</v>
       </c>
       <c r="AN38" t="s" s="2">
-        <v>339</v>
+        <v>350</v>
       </c>
       <c r="AO38" t="s" s="2">
-        <v>79</v>
+        <v>351</v>
       </c>
       <c r="AP38" t="s" s="2">
-        <v>79</v>
+        <v>352</v>
       </c>
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>340</v>
+        <v>353</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>340</v>
+        <v>353</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
-        <v>341</v>
+        <v>79</v>
       </c>
       <c r="E39" s="2"/>
       <c r="F39" t="s" s="2">
@@ -7069,19 +7064,19 @@
         <v>90</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>254</v>
+        <v>354</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>342</v>
+        <v>355</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>343</v>
+        <v>356</v>
       </c>
       <c r="N39" t="s" s="2">
-        <v>344</v>
+        <v>357</v>
       </c>
       <c r="O39" t="s" s="2">
-        <v>345</v>
+        <v>358</v>
       </c>
       <c r="P39" t="s" s="2">
         <v>79</v>
@@ -7091,7 +7086,7 @@
         <v>79</v>
       </c>
       <c r="S39" t="s" s="2">
-        <v>346</v>
+        <v>79</v>
       </c>
       <c r="T39" t="s" s="2">
         <v>79</v>
@@ -7106,13 +7101,13 @@
         <v>79</v>
       </c>
       <c r="X39" t="s" s="2">
-        <v>150</v>
+        <v>79</v>
       </c>
       <c r="Y39" t="s" s="2">
-        <v>347</v>
+        <v>79</v>
       </c>
       <c r="Z39" t="s" s="2">
-        <v>348</v>
+        <v>79</v>
       </c>
       <c r="AA39" t="s" s="2">
         <v>79</v>
@@ -7130,10 +7125,10 @@
         <v>79</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>340</v>
+        <v>353</v>
       </c>
       <c r="AG39" t="s" s="2">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="AH39" t="s" s="2">
         <v>89</v>
@@ -7142,33 +7137,33 @@
         <v>101</v>
       </c>
       <c r="AJ39" t="s" s="2">
-        <v>125</v>
+        <v>225</v>
       </c>
       <c r="AK39" t="s" s="2">
-        <v>349</v>
+        <v>359</v>
       </c>
       <c r="AL39" t="s" s="2">
-        <v>350</v>
+        <v>79</v>
       </c>
       <c r="AM39" t="s" s="2">
-        <v>351</v>
+        <v>360</v>
       </c>
       <c r="AN39" t="s" s="2">
-        <v>352</v>
+        <v>361</v>
       </c>
       <c r="AO39" t="s" s="2">
-        <v>353</v>
+        <v>362</v>
       </c>
       <c r="AP39" t="s" s="2">
-        <v>354</v>
+        <v>79</v>
       </c>
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>355</v>
+        <v>363</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>355</v>
+        <v>363</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -7176,13 +7171,13 @@
       </c>
       <c r="E40" s="2"/>
       <c r="F40" t="s" s="2">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="G40" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="H40" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="I40" t="s" s="2">
         <v>79</v>
@@ -7191,20 +7186,18 @@
         <v>90</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>357</v>
+        <v>365</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>358</v>
+        <v>366</v>
       </c>
       <c r="N40" t="s" s="2">
-        <v>359</v>
-      </c>
-      <c r="O40" t="s" s="2">
-        <v>360</v>
-      </c>
+        <v>367</v>
+      </c>
+      <c r="O40" s="2"/>
       <c r="P40" t="s" s="2">
         <v>79</v>
       </c>
@@ -7252,34 +7245,34 @@
         <v>79</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>355</v>
+        <v>363</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH40" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="AI40" t="s" s="2">
         <v>101</v>
       </c>
       <c r="AJ40" t="s" s="2">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="AK40" t="s" s="2">
-        <v>361</v>
+        <v>79</v>
       </c>
       <c r="AL40" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AM40" t="s" s="2">
+        <v>349</v>
+      </c>
+      <c r="AN40" t="s" s="2">
+        <v>368</v>
+      </c>
+      <c r="AO40" t="s" s="2">
         <v>362</v>
-      </c>
-      <c r="AN40" t="s" s="2">
-        <v>363</v>
-      </c>
-      <c r="AO40" t="s" s="2">
-        <v>364</v>
       </c>
       <c r="AP40" t="s" s="2">
         <v>79</v>
@@ -7287,21 +7280,21 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>365</v>
+        <v>369</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>365</v>
+        <v>369</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
-        <v>79</v>
+        <v>370</v>
       </c>
       <c r="E41" s="2"/>
       <c r="F41" t="s" s="2">
         <v>77</v>
       </c>
       <c r="G41" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="H41" t="s" s="2">
         <v>79</v>
@@ -7313,18 +7306,20 @@
         <v>90</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>366</v>
+        <v>371</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>367</v>
+        <v>372</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>368</v>
+        <v>373</v>
       </c>
       <c r="N41" t="s" s="2">
-        <v>369</v>
-      </c>
-      <c r="O41" s="2"/>
+        <v>374</v>
+      </c>
+      <c r="O41" t="s" s="2">
+        <v>375</v>
+      </c>
       <c r="P41" t="s" s="2">
         <v>79</v>
       </c>
@@ -7372,34 +7367,34 @@
         <v>79</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>365</v>
+        <v>369</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH41" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="AI41" t="s" s="2">
         <v>101</v>
       </c>
       <c r="AJ41" t="s" s="2">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="AK41" t="s" s="2">
-        <v>79</v>
+        <v>376</v>
       </c>
       <c r="AL41" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AM41" t="s" s="2">
-        <v>351</v>
+        <v>377</v>
       </c>
       <c r="AN41" t="s" s="2">
-        <v>370</v>
+        <v>378</v>
       </c>
       <c r="AO41" t="s" s="2">
-        <v>364</v>
+        <v>379</v>
       </c>
       <c r="AP41" t="s" s="2">
         <v>79</v>
@@ -7407,24 +7402,24 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>371</v>
+        <v>380</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>371</v>
+        <v>380</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
-        <v>372</v>
+        <v>381</v>
       </c>
       <c r="E42" s="2"/>
       <c r="F42" t="s" s="2">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="G42" t="s" s="2">
         <v>89</v>
       </c>
       <c r="H42" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="I42" t="s" s="2">
         <v>79</v>
@@ -7433,19 +7428,19 @@
         <v>90</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>373</v>
+        <v>382</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>374</v>
+        <v>383</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>375</v>
+        <v>384</v>
       </c>
       <c r="N42" t="s" s="2">
-        <v>376</v>
+        <v>385</v>
       </c>
       <c r="O42" t="s" s="2">
-        <v>377</v>
+        <v>386</v>
       </c>
       <c r="P42" t="s" s="2">
         <v>79</v>
@@ -7494,7 +7489,7 @@
         <v>79</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>371</v>
+        <v>380</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>77</v>
@@ -7503,25 +7498,25 @@
         <v>89</v>
       </c>
       <c r="AI42" t="s" s="2">
-        <v>101</v>
+        <v>387</v>
       </c>
       <c r="AJ42" t="s" s="2">
-        <v>227</v>
+        <v>388</v>
       </c>
       <c r="AK42" t="s" s="2">
-        <v>378</v>
+        <v>389</v>
       </c>
       <c r="AL42" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AM42" t="s" s="2">
-        <v>379</v>
+        <v>390</v>
       </c>
       <c r="AN42" t="s" s="2">
-        <v>380</v>
+        <v>391</v>
       </c>
       <c r="AO42" t="s" s="2">
-        <v>381</v>
+        <v>392</v>
       </c>
       <c r="AP42" t="s" s="2">
         <v>79</v>
@@ -7529,24 +7524,24 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>382</v>
+        <v>393</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>382</v>
+        <v>393</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
-        <v>383</v>
+        <v>79</v>
       </c>
       <c r="E43" s="2"/>
       <c r="F43" t="s" s="2">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="G43" t="s" s="2">
         <v>89</v>
       </c>
       <c r="H43" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="I43" t="s" s="2">
         <v>79</v>
@@ -7555,20 +7550,18 @@
         <v>90</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>384</v>
+        <v>127</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>385</v>
+        <v>394</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>386</v>
+        <v>395</v>
       </c>
       <c r="N43" t="s" s="2">
-        <v>387</v>
-      </c>
-      <c r="O43" t="s" s="2">
-        <v>388</v>
-      </c>
+        <v>396</v>
+      </c>
+      <c r="O43" s="2"/>
       <c r="P43" t="s" s="2">
         <v>79</v>
       </c>
@@ -7616,7 +7609,7 @@
         <v>79</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>382</v>
+        <v>393</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>77</v>
@@ -7625,25 +7618,25 @@
         <v>89</v>
       </c>
       <c r="AI43" t="s" s="2">
-        <v>389</v>
+        <v>101</v>
       </c>
       <c r="AJ43" t="s" s="2">
-        <v>390</v>
+        <v>102</v>
       </c>
       <c r="AK43" t="s" s="2">
-        <v>391</v>
+        <v>79</v>
       </c>
       <c r="AL43" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AM43" t="s" s="2">
-        <v>392</v>
+        <v>397</v>
       </c>
       <c r="AN43" t="s" s="2">
-        <v>393</v>
+        <v>398</v>
       </c>
       <c r="AO43" t="s" s="2">
-        <v>394</v>
+        <v>399</v>
       </c>
       <c r="AP43" t="s" s="2">
         <v>79</v>
@@ -7651,10 +7644,10 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>395</v>
+        <v>400</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>395</v>
+        <v>400</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -7665,7 +7658,7 @@
         <v>77</v>
       </c>
       <c r="G44" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="H44" t="s" s="2">
         <v>79</v>
@@ -7677,18 +7670,20 @@
         <v>90</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>127</v>
+        <v>401</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>396</v>
+        <v>402</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>397</v>
+        <v>403</v>
       </c>
       <c r="N44" t="s" s="2">
-        <v>398</v>
-      </c>
-      <c r="O44" s="2"/>
+        <v>223</v>
+      </c>
+      <c r="O44" t="s" s="2">
+        <v>404</v>
+      </c>
       <c r="P44" t="s" s="2">
         <v>79</v>
       </c>
@@ -7736,34 +7731,34 @@
         <v>79</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>395</v>
+        <v>400</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH44" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="AI44" t="s" s="2">
         <v>101</v>
       </c>
       <c r="AJ44" t="s" s="2">
-        <v>125</v>
+        <v>225</v>
       </c>
       <c r="AK44" t="s" s="2">
-        <v>79</v>
+        <v>405</v>
       </c>
       <c r="AL44" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AM44" t="s" s="2">
-        <v>399</v>
+        <v>406</v>
       </c>
       <c r="AN44" t="s" s="2">
-        <v>400</v>
+        <v>407</v>
       </c>
       <c r="AO44" t="s" s="2">
-        <v>401</v>
+        <v>408</v>
       </c>
       <c r="AP44" t="s" s="2">
         <v>79</v>
@@ -7771,10 +7766,10 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>402</v>
+        <v>409</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>402</v>
+        <v>409</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7785,10 +7780,10 @@
         <v>77</v>
       </c>
       <c r="G45" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="H45" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="I45" t="s" s="2">
         <v>79</v>
@@ -7797,19 +7792,19 @@
         <v>90</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>403</v>
+        <v>410</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>404</v>
+        <v>411</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>405</v>
+        <v>411</v>
       </c>
       <c r="N45" t="s" s="2">
-        <v>225</v>
+        <v>412</v>
       </c>
       <c r="O45" t="s" s="2">
-        <v>406</v>
+        <v>413</v>
       </c>
       <c r="P45" t="s" s="2">
         <v>79</v>
@@ -7846,59 +7841,59 @@
         <v>79</v>
       </c>
       <c r="AB45" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC45" t="s" s="2">
-        <v>79</v>
-      </c>
+        <v>414</v>
+      </c>
+      <c r="AC45" s="2"/>
       <c r="AD45" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AE45" t="s" s="2">
-        <v>79</v>
+        <v>415</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>402</v>
+        <v>409</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH45" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="AI45" t="s" s="2">
-        <v>101</v>
+        <v>416</v>
       </c>
       <c r="AJ45" t="s" s="2">
-        <v>227</v>
+        <v>102</v>
       </c>
       <c r="AK45" t="s" s="2">
-        <v>407</v>
+        <v>79</v>
       </c>
       <c r="AL45" t="s" s="2">
-        <v>79</v>
+        <v>417</v>
       </c>
       <c r="AM45" t="s" s="2">
-        <v>408</v>
+        <v>418</v>
       </c>
       <c r="AN45" t="s" s="2">
-        <v>409</v>
+        <v>419</v>
       </c>
       <c r="AO45" t="s" s="2">
-        <v>410</v>
+        <v>79</v>
       </c>
       <c r="AP45" t="s" s="2">
-        <v>79</v>
+        <v>420</v>
       </c>
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>411</v>
+        <v>421</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>411</v>
-      </c>
-      <c r="C46" s="2"/>
+        <v>409</v>
+      </c>
+      <c r="C46" t="s" s="2">
+        <v>422</v>
+      </c>
       <c r="D46" t="s" s="2">
         <v>79</v>
       </c>
@@ -7919,19 +7914,19 @@
         <v>90</v>
       </c>
       <c r="K46" t="s" s="2">
+        <v>410</v>
+      </c>
+      <c r="L46" t="s" s="2">
+        <v>411</v>
+      </c>
+      <c r="M46" t="s" s="2">
+        <v>411</v>
+      </c>
+      <c r="N46" t="s" s="2">
         <v>412</v>
       </c>
-      <c r="L46" t="s" s="2">
+      <c r="O46" t="s" s="2">
         <v>413</v>
-      </c>
-      <c r="M46" t="s" s="2">
-        <v>413</v>
-      </c>
-      <c r="N46" t="s" s="2">
-        <v>414</v>
-      </c>
-      <c r="O46" t="s" s="2">
-        <v>415</v>
       </c>
       <c r="P46" t="s" s="2">
         <v>79</v>
@@ -7968,17 +7963,19 @@
         <v>79</v>
       </c>
       <c r="AB46" t="s" s="2">
-        <v>416</v>
-      </c>
-      <c r="AC46" s="2"/>
+        <v>79</v>
+      </c>
+      <c r="AC46" t="s" s="2">
+        <v>79</v>
+      </c>
       <c r="AD46" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AE46" t="s" s="2">
-        <v>417</v>
+        <v>79</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>411</v>
+        <v>409</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>77</v>
@@ -7987,28 +7984,28 @@
         <v>89</v>
       </c>
       <c r="AI46" t="s" s="2">
+        <v>416</v>
+      </c>
+      <c r="AJ46" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK46" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AL46" t="s" s="2">
+        <v>417</v>
+      </c>
+      <c r="AM46" t="s" s="2">
         <v>418</v>
       </c>
-      <c r="AJ46" t="s" s="2">
-        <v>125</v>
-      </c>
-      <c r="AK46" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AL46" t="s" s="2">
+      <c r="AN46" t="s" s="2">
         <v>419</v>
       </c>
-      <c r="AM46" t="s" s="2">
+      <c r="AO46" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AP46" t="s" s="2">
         <v>420</v>
-      </c>
-      <c r="AN46" t="s" s="2">
-        <v>421</v>
-      </c>
-      <c r="AO46" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AP46" t="s" s="2">
-        <v>422</v>
       </c>
     </row>
     <row r="47" hidden="true">
@@ -8016,11 +8013,9 @@
         <v>423</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>411</v>
-      </c>
-      <c r="C47" t="s" s="2">
         <v>424</v>
       </c>
+      <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
         <v>79</v>
       </c>
@@ -8032,29 +8027,25 @@
         <v>89</v>
       </c>
       <c r="H47" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="I47" t="s" s="2">
         <v>79</v>
       </c>
       <c r="J47" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>412</v>
+        <v>105</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>413</v>
+        <v>106</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>413</v>
-      </c>
-      <c r="N47" t="s" s="2">
-        <v>414</v>
-      </c>
-      <c r="O47" t="s" s="2">
-        <v>415</v>
-      </c>
+        <v>107</v>
+      </c>
+      <c r="N47" s="2"/>
+      <c r="O47" s="2"/>
       <c r="P47" t="s" s="2">
         <v>79</v>
       </c>
@@ -8102,7 +8093,7 @@
         <v>79</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>411</v>
+        <v>108</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>77</v>
@@ -8111,28 +8102,28 @@
         <v>89</v>
       </c>
       <c r="AI47" t="s" s="2">
-        <v>418</v>
+        <v>79</v>
       </c>
       <c r="AJ47" t="s" s="2">
-        <v>125</v>
+        <v>79</v>
       </c>
       <c r="AK47" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL47" t="s" s="2">
-        <v>419</v>
+        <v>79</v>
       </c>
       <c r="AM47" t="s" s="2">
-        <v>420</v>
+        <v>79</v>
       </c>
       <c r="AN47" t="s" s="2">
-        <v>421</v>
+        <v>109</v>
       </c>
       <c r="AO47" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AP47" t="s" s="2">
-        <v>422</v>
+        <v>79</v>
       </c>
     </row>
     <row r="48" hidden="true">
@@ -8144,14 +8135,14 @@
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
-        <v>79</v>
+        <v>111</v>
       </c>
       <c r="E48" s="2"/>
       <c r="F48" t="s" s="2">
         <v>77</v>
       </c>
       <c r="G48" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="H48" t="s" s="2">
         <v>79</v>
@@ -8163,15 +8154,17 @@
         <v>79</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>104</v>
+        <v>112</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>105</v>
+        <v>113</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>106</v>
-      </c>
-      <c r="N48" s="2"/>
+        <v>114</v>
+      </c>
+      <c r="N48" t="s" s="2">
+        <v>115</v>
+      </c>
       <c r="O48" s="2"/>
       <c r="P48" t="s" s="2">
         <v>79</v>
@@ -8208,31 +8201,31 @@
         <v>79</v>
       </c>
       <c r="AB48" t="s" s="2">
-        <v>79</v>
+        <v>116</v>
       </c>
       <c r="AC48" t="s" s="2">
-        <v>79</v>
+        <v>117</v>
       </c>
       <c r="AD48" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AE48" t="s" s="2">
-        <v>79</v>
+        <v>118</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>107</v>
+        <v>119</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH48" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="AI48" t="s" s="2">
-        <v>79</v>
+        <v>101</v>
       </c>
       <c r="AJ48" t="s" s="2">
-        <v>79</v>
+        <v>120</v>
       </c>
       <c r="AK48" t="s" s="2">
         <v>79</v>
@@ -8244,7 +8237,7 @@
         <v>79</v>
       </c>
       <c r="AN48" t="s" s="2">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="AO48" t="s" s="2">
         <v>79</v>
@@ -8262,14 +8255,14 @@
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
-        <v>110</v>
+        <v>79</v>
       </c>
       <c r="E49" s="2"/>
       <c r="F49" t="s" s="2">
         <v>77</v>
       </c>
       <c r="G49" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="H49" t="s" s="2">
         <v>79</v>
@@ -8278,21 +8271,23 @@
         <v>79</v>
       </c>
       <c r="J49" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>111</v>
+        <v>429</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>112</v>
+        <v>430</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>113</v>
+        <v>431</v>
       </c>
       <c r="N49" t="s" s="2">
-        <v>114</v>
-      </c>
-      <c r="O49" s="2"/>
+        <v>432</v>
+      </c>
+      <c r="O49" t="s" s="2">
+        <v>433</v>
+      </c>
       <c r="P49" t="s" s="2">
         <v>79</v>
       </c>
@@ -8328,31 +8323,31 @@
         <v>79</v>
       </c>
       <c r="AB49" t="s" s="2">
-        <v>115</v>
+        <v>79</v>
       </c>
       <c r="AC49" t="s" s="2">
-        <v>116</v>
+        <v>79</v>
       </c>
       <c r="AD49" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AE49" t="s" s="2">
-        <v>117</v>
+        <v>79</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>118</v>
+        <v>434</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH49" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="AI49" t="s" s="2">
         <v>101</v>
       </c>
       <c r="AJ49" t="s" s="2">
-        <v>119</v>
+        <v>102</v>
       </c>
       <c r="AK49" t="s" s="2">
         <v>79</v>
@@ -8361,10 +8356,10 @@
         <v>79</v>
       </c>
       <c r="AM49" t="s" s="2">
-        <v>79</v>
+        <v>435</v>
       </c>
       <c r="AN49" t="s" s="2">
-        <v>102</v>
+        <v>436</v>
       </c>
       <c r="AO49" t="s" s="2">
         <v>79</v>
@@ -8375,10 +8370,10 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>429</v>
+        <v>437</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>430</v>
+        <v>438</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -8395,30 +8390,32 @@
         <v>79</v>
       </c>
       <c r="I50" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="J50" t="s" s="2">
         <v>90</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>431</v>
+        <v>168</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>432</v>
+        <v>439</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>433</v>
+        <v>440</v>
       </c>
       <c r="N50" t="s" s="2">
-        <v>434</v>
+        <v>304</v>
       </c>
       <c r="O50" t="s" s="2">
-        <v>435</v>
+        <v>441</v>
       </c>
       <c r="P50" t="s" s="2">
         <v>79</v>
       </c>
-      <c r="Q50" s="2"/>
+      <c r="Q50" t="s" s="2">
+        <v>442</v>
+      </c>
       <c r="R50" t="s" s="2">
         <v>79</v>
       </c>
@@ -8438,13 +8435,13 @@
         <v>79</v>
       </c>
       <c r="X50" t="s" s="2">
-        <v>79</v>
+        <v>243</v>
       </c>
       <c r="Y50" t="s" s="2">
-        <v>79</v>
+        <v>443</v>
       </c>
       <c r="Z50" t="s" s="2">
-        <v>79</v>
+        <v>444</v>
       </c>
       <c r="AA50" t="s" s="2">
         <v>79</v>
@@ -8462,7 +8459,7 @@
         <v>79</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>436</v>
+        <v>445</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>77</v>
@@ -8474,7 +8471,7 @@
         <v>101</v>
       </c>
       <c r="AJ50" t="s" s="2">
-        <v>125</v>
+        <v>102</v>
       </c>
       <c r="AK50" t="s" s="2">
         <v>79</v>
@@ -8483,10 +8480,10 @@
         <v>79</v>
       </c>
       <c r="AM50" t="s" s="2">
-        <v>437</v>
+        <v>446</v>
       </c>
       <c r="AN50" t="s" s="2">
-        <v>438</v>
+        <v>447</v>
       </c>
       <c r="AO50" t="s" s="2">
         <v>79</v>
@@ -8497,10 +8494,10 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>439</v>
+        <v>448</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>440</v>
+        <v>449</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -8508,7 +8505,7 @@
       </c>
       <c r="E51" s="2"/>
       <c r="F51" t="s" s="2">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="G51" t="s" s="2">
         <v>89</v>
@@ -8517,37 +8514,35 @@
         <v>79</v>
       </c>
       <c r="I51" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="J51" t="s" s="2">
         <v>90</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>170</v>
+        <v>105</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>441</v>
+        <v>450</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>442</v>
+        <v>451</v>
       </c>
       <c r="N51" t="s" s="2">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="O51" t="s" s="2">
-        <v>443</v>
+        <v>452</v>
       </c>
       <c r="P51" t="s" s="2">
         <v>79</v>
       </c>
-      <c r="Q51" t="s" s="2">
-        <v>444</v>
-      </c>
+      <c r="Q51" s="2"/>
       <c r="R51" t="s" s="2">
         <v>79</v>
       </c>
       <c r="S51" t="s" s="2">
-        <v>79</v>
+        <v>453</v>
       </c>
       <c r="T51" t="s" s="2">
         <v>79</v>
@@ -8562,13 +8557,13 @@
         <v>79</v>
       </c>
       <c r="X51" t="s" s="2">
-        <v>245</v>
+        <v>79</v>
       </c>
       <c r="Y51" t="s" s="2">
-        <v>445</v>
+        <v>79</v>
       </c>
       <c r="Z51" t="s" s="2">
-        <v>446</v>
+        <v>79</v>
       </c>
       <c r="AA51" t="s" s="2">
         <v>79</v>
@@ -8586,7 +8581,7 @@
         <v>79</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>447</v>
+        <v>454</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>77</v>
@@ -8598,7 +8593,7 @@
         <v>101</v>
       </c>
       <c r="AJ51" t="s" s="2">
-        <v>125</v>
+        <v>102</v>
       </c>
       <c r="AK51" t="s" s="2">
         <v>79</v>
@@ -8607,10 +8602,10 @@
         <v>79</v>
       </c>
       <c r="AM51" t="s" s="2">
-        <v>448</v>
+        <v>455</v>
       </c>
       <c r="AN51" t="s" s="2">
-        <v>449</v>
+        <v>456</v>
       </c>
       <c r="AO51" t="s" s="2">
         <v>79</v>
@@ -8621,10 +8616,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>450</v>
+        <v>457</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>451</v>
+        <v>458</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -8632,7 +8627,7 @@
       </c>
       <c r="E52" s="2"/>
       <c r="F52" t="s" s="2">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="G52" t="s" s="2">
         <v>89</v>
@@ -8647,19 +8642,19 @@
         <v>90</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>104</v>
+        <v>133</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>452</v>
+        <v>459</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>453</v>
+        <v>460</v>
       </c>
       <c r="N52" t="s" s="2">
-        <v>306</v>
+        <v>461</v>
       </c>
       <c r="O52" t="s" s="2">
-        <v>454</v>
+        <v>462</v>
       </c>
       <c r="P52" t="s" s="2">
         <v>79</v>
@@ -8669,7 +8664,7 @@
         <v>79</v>
       </c>
       <c r="S52" t="s" s="2">
-        <v>455</v>
+        <v>463</v>
       </c>
       <c r="T52" t="s" s="2">
         <v>79</v>
@@ -8708,7 +8703,7 @@
         <v>79</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>456</v>
+        <v>464</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>77</v>
@@ -8717,10 +8712,10 @@
         <v>89</v>
       </c>
       <c r="AI52" t="s" s="2">
-        <v>101</v>
+        <v>465</v>
       </c>
       <c r="AJ52" t="s" s="2">
-        <v>125</v>
+        <v>102</v>
       </c>
       <c r="AK52" t="s" s="2">
         <v>79</v>
@@ -8729,10 +8724,10 @@
         <v>79</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>457</v>
+        <v>455</v>
       </c>
       <c r="AN52" t="s" s="2">
-        <v>458</v>
+        <v>466</v>
       </c>
       <c r="AO52" t="s" s="2">
         <v>79</v>
@@ -8743,10 +8738,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>459</v>
+        <v>467</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>460</v>
+        <v>468</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8754,7 +8749,7 @@
       </c>
       <c r="E53" s="2"/>
       <c r="F53" t="s" s="2">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="G53" t="s" s="2">
         <v>89</v>
@@ -8769,19 +8764,19 @@
         <v>90</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>133</v>
+        <v>168</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>461</v>
+        <v>469</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>462</v>
+        <v>470</v>
       </c>
       <c r="N53" t="s" s="2">
-        <v>463</v>
+        <v>471</v>
       </c>
       <c r="O53" t="s" s="2">
-        <v>464</v>
+        <v>472</v>
       </c>
       <c r="P53" t="s" s="2">
         <v>79</v>
@@ -8791,7 +8786,7 @@
         <v>79</v>
       </c>
       <c r="S53" t="s" s="2">
-        <v>465</v>
+        <v>89</v>
       </c>
       <c r="T53" t="s" s="2">
         <v>79</v>
@@ -8830,7 +8825,7 @@
         <v>79</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>466</v>
+        <v>473</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>77</v>
@@ -8839,10 +8834,10 @@
         <v>89</v>
       </c>
       <c r="AI53" t="s" s="2">
-        <v>467</v>
+        <v>101</v>
       </c>
       <c r="AJ53" t="s" s="2">
-        <v>125</v>
+        <v>102</v>
       </c>
       <c r="AK53" t="s" s="2">
         <v>79</v>
@@ -8851,10 +8846,10 @@
         <v>79</v>
       </c>
       <c r="AM53" t="s" s="2">
-        <v>457</v>
+        <v>455</v>
       </c>
       <c r="AN53" t="s" s="2">
-        <v>468</v>
+        <v>474</v>
       </c>
       <c r="AO53" t="s" s="2">
         <v>79</v>
@@ -8865,10 +8860,10 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>469</v>
+        <v>475</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>470</v>
+        <v>475</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8876,34 +8871,34 @@
       </c>
       <c r="E54" s="2"/>
       <c r="F54" t="s" s="2">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="G54" t="s" s="2">
         <v>89</v>
       </c>
       <c r="H54" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="I54" t="s" s="2">
         <v>79</v>
       </c>
       <c r="J54" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>170</v>
+        <v>252</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>471</v>
+        <v>476</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>472</v>
+        <v>477</v>
       </c>
       <c r="N54" t="s" s="2">
-        <v>473</v>
+        <v>478</v>
       </c>
       <c r="O54" t="s" s="2">
-        <v>474</v>
+        <v>479</v>
       </c>
       <c r="P54" t="s" s="2">
         <v>79</v>
@@ -8913,7 +8908,7 @@
         <v>79</v>
       </c>
       <c r="S54" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="T54" t="s" s="2">
         <v>79</v>
@@ -8928,13 +8923,13 @@
         <v>79</v>
       </c>
       <c r="X54" t="s" s="2">
-        <v>79</v>
+        <v>148</v>
       </c>
       <c r="Y54" t="s" s="2">
-        <v>79</v>
+        <v>480</v>
       </c>
       <c r="Z54" t="s" s="2">
-        <v>79</v>
+        <v>481</v>
       </c>
       <c r="AA54" t="s" s="2">
         <v>79</v>
@@ -8961,10 +8956,10 @@
         <v>89</v>
       </c>
       <c r="AI54" t="s" s="2">
-        <v>101</v>
+        <v>482</v>
       </c>
       <c r="AJ54" t="s" s="2">
-        <v>125</v>
+        <v>102</v>
       </c>
       <c r="AK54" t="s" s="2">
         <v>79</v>
@@ -8973,10 +8968,10 @@
         <v>79</v>
       </c>
       <c r="AM54" t="s" s="2">
-        <v>457</v>
+        <v>103</v>
       </c>
       <c r="AN54" t="s" s="2">
-        <v>476</v>
+        <v>483</v>
       </c>
       <c r="AO54" t="s" s="2">
         <v>79</v>
@@ -8987,10 +8982,10 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>477</v>
+        <v>484</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>477</v>
+        <v>484</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -9004,7 +8999,7 @@
         <v>89</v>
       </c>
       <c r="H55" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="I55" t="s" s="2">
         <v>79</v>
@@ -9013,20 +9008,16 @@
         <v>79</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>254</v>
+        <v>105</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>478</v>
+        <v>106</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>479</v>
-      </c>
-      <c r="N55" t="s" s="2">
-        <v>480</v>
-      </c>
-      <c r="O55" t="s" s="2">
-        <v>481</v>
-      </c>
+        <v>107</v>
+      </c>
+      <c r="N55" s="2"/>
+      <c r="O55" s="2"/>
       <c r="P55" t="s" s="2">
         <v>79</v>
       </c>
@@ -9050,13 +9041,13 @@
         <v>79</v>
       </c>
       <c r="X55" t="s" s="2">
-        <v>150</v>
+        <v>79</v>
       </c>
       <c r="Y55" t="s" s="2">
-        <v>482</v>
+        <v>79</v>
       </c>
       <c r="Z55" t="s" s="2">
-        <v>483</v>
+        <v>79</v>
       </c>
       <c r="AA55" t="s" s="2">
         <v>79</v>
@@ -9074,7 +9065,7 @@
         <v>79</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>477</v>
+        <v>108</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>77</v>
@@ -9083,10 +9074,10 @@
         <v>89</v>
       </c>
       <c r="AI55" t="s" s="2">
-        <v>484</v>
+        <v>79</v>
       </c>
       <c r="AJ55" t="s" s="2">
-        <v>125</v>
+        <v>79</v>
       </c>
       <c r="AK55" t="s" s="2">
         <v>79</v>
@@ -9095,10 +9086,10 @@
         <v>79</v>
       </c>
       <c r="AM55" t="s" s="2">
-        <v>102</v>
+        <v>79</v>
       </c>
       <c r="AN55" t="s" s="2">
-        <v>485</v>
+        <v>109</v>
       </c>
       <c r="AO55" t="s" s="2">
         <v>79</v>
@@ -9109,21 +9100,21 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
-        <v>79</v>
+        <v>111</v>
       </c>
       <c r="E56" s="2"/>
       <c r="F56" t="s" s="2">
         <v>77</v>
       </c>
       <c r="G56" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="H56" t="s" s="2">
         <v>79</v>
@@ -9135,15 +9126,17 @@
         <v>79</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>104</v>
+        <v>112</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>105</v>
+        <v>113</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>106</v>
-      </c>
-      <c r="N56" s="2"/>
+        <v>114</v>
+      </c>
+      <c r="N56" t="s" s="2">
+        <v>115</v>
+      </c>
       <c r="O56" s="2"/>
       <c r="P56" t="s" s="2">
         <v>79</v>
@@ -9180,31 +9173,31 @@
         <v>79</v>
       </c>
       <c r="AB56" t="s" s="2">
-        <v>79</v>
+        <v>116</v>
       </c>
       <c r="AC56" t="s" s="2">
-        <v>79</v>
+        <v>117</v>
       </c>
       <c r="AD56" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AE56" t="s" s="2">
-        <v>79</v>
+        <v>118</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>107</v>
+        <v>119</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH56" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="AI56" t="s" s="2">
-        <v>79</v>
+        <v>101</v>
       </c>
       <c r="AJ56" t="s" s="2">
-        <v>79</v>
+        <v>120</v>
       </c>
       <c r="AK56" t="s" s="2">
         <v>79</v>
@@ -9216,7 +9209,7 @@
         <v>79</v>
       </c>
       <c r="AN56" t="s" s="2">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="AO56" t="s" s="2">
         <v>79</v>
@@ -9227,14 +9220,14 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
-        <v>110</v>
+        <v>79</v>
       </c>
       <c r="E57" s="2"/>
       <c r="F57" t="s" s="2">
@@ -9250,21 +9243,23 @@
         <v>79</v>
       </c>
       <c r="J57" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>111</v>
+        <v>144</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>112</v>
+        <v>271</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>113</v>
+        <v>272</v>
       </c>
       <c r="N57" t="s" s="2">
-        <v>114</v>
-      </c>
-      <c r="O57" s="2"/>
+        <v>273</v>
+      </c>
+      <c r="O57" t="s" s="2">
+        <v>274</v>
+      </c>
       <c r="P57" t="s" s="2">
         <v>79</v>
       </c>
@@ -9300,19 +9295,19 @@
         <v>79</v>
       </c>
       <c r="AB57" t="s" s="2">
-        <v>115</v>
+        <v>79</v>
       </c>
       <c r="AC57" t="s" s="2">
-        <v>116</v>
+        <v>79</v>
       </c>
       <c r="AD57" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AE57" t="s" s="2">
-        <v>117</v>
+        <v>79</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>118</v>
+        <v>275</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>77</v>
@@ -9324,7 +9319,7 @@
         <v>101</v>
       </c>
       <c r="AJ57" t="s" s="2">
-        <v>119</v>
+        <v>102</v>
       </c>
       <c r="AK57" t="s" s="2">
         <v>79</v>
@@ -9333,10 +9328,10 @@
         <v>79</v>
       </c>
       <c r="AM57" t="s" s="2">
-        <v>79</v>
+        <v>276</v>
       </c>
       <c r="AN57" t="s" s="2">
-        <v>102</v>
+        <v>277</v>
       </c>
       <c r="AO57" t="s" s="2">
         <v>79</v>
@@ -9347,10 +9342,10 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -9361,7 +9356,7 @@
         <v>77</v>
       </c>
       <c r="G58" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="H58" t="s" s="2">
         <v>79</v>
@@ -9370,23 +9365,19 @@
         <v>79</v>
       </c>
       <c r="J58" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>146</v>
+        <v>105</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>273</v>
+        <v>106</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>274</v>
-      </c>
-      <c r="N58" t="s" s="2">
-        <v>275</v>
-      </c>
-      <c r="O58" t="s" s="2">
-        <v>276</v>
-      </c>
+        <v>107</v>
+      </c>
+      <c r="N58" s="2"/>
+      <c r="O58" s="2"/>
       <c r="P58" t="s" s="2">
         <v>79</v>
       </c>
@@ -9434,19 +9425,19 @@
         <v>79</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>277</v>
+        <v>108</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH58" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="AI58" t="s" s="2">
-        <v>101</v>
+        <v>79</v>
       </c>
       <c r="AJ58" t="s" s="2">
-        <v>125</v>
+        <v>79</v>
       </c>
       <c r="AK58" t="s" s="2">
         <v>79</v>
@@ -9455,10 +9446,10 @@
         <v>79</v>
       </c>
       <c r="AM58" t="s" s="2">
-        <v>278</v>
+        <v>79</v>
       </c>
       <c r="AN58" t="s" s="2">
-        <v>279</v>
+        <v>109</v>
       </c>
       <c r="AO58" t="s" s="2">
         <v>79</v>
@@ -9469,21 +9460,21 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
-        <v>79</v>
+        <v>111</v>
       </c>
       <c r="E59" s="2"/>
       <c r="F59" t="s" s="2">
         <v>77</v>
       </c>
       <c r="G59" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="H59" t="s" s="2">
         <v>79</v>
@@ -9495,15 +9486,17 @@
         <v>79</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>104</v>
+        <v>112</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>105</v>
+        <v>113</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>106</v>
-      </c>
-      <c r="N59" s="2"/>
+        <v>114</v>
+      </c>
+      <c r="N59" t="s" s="2">
+        <v>115</v>
+      </c>
       <c r="O59" s="2"/>
       <c r="P59" t="s" s="2">
         <v>79</v>
@@ -9540,31 +9533,31 @@
         <v>79</v>
       </c>
       <c r="AB59" t="s" s="2">
-        <v>79</v>
+        <v>116</v>
       </c>
       <c r="AC59" t="s" s="2">
-        <v>79</v>
+        <v>117</v>
       </c>
       <c r="AD59" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AE59" t="s" s="2">
-        <v>79</v>
+        <v>118</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>107</v>
+        <v>119</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH59" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="AI59" t="s" s="2">
-        <v>79</v>
+        <v>101</v>
       </c>
       <c r="AJ59" t="s" s="2">
-        <v>79</v>
+        <v>120</v>
       </c>
       <c r="AK59" t="s" s="2">
         <v>79</v>
@@ -9576,7 +9569,7 @@
         <v>79</v>
       </c>
       <c r="AN59" t="s" s="2">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="AO59" t="s" s="2">
         <v>79</v>
@@ -9587,21 +9580,21 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
-        <v>110</v>
+        <v>79</v>
       </c>
       <c r="E60" s="2"/>
       <c r="F60" t="s" s="2">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="G60" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="H60" t="s" s="2">
         <v>79</v>
@@ -9610,21 +9603,23 @@
         <v>79</v>
       </c>
       <c r="J60" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>111</v>
+        <v>133</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>112</v>
+        <v>284</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>113</v>
+        <v>285</v>
       </c>
       <c r="N60" t="s" s="2">
-        <v>114</v>
-      </c>
-      <c r="O60" s="2"/>
+        <v>286</v>
+      </c>
+      <c r="O60" t="s" s="2">
+        <v>287</v>
+      </c>
       <c r="P60" t="s" s="2">
         <v>79</v>
       </c>
@@ -9660,31 +9655,31 @@
         <v>79</v>
       </c>
       <c r="AB60" t="s" s="2">
-        <v>115</v>
+        <v>79</v>
       </c>
       <c r="AC60" t="s" s="2">
-        <v>116</v>
+        <v>79</v>
       </c>
       <c r="AD60" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AE60" t="s" s="2">
-        <v>117</v>
+        <v>79</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>118</v>
+        <v>289</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH60" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="AI60" t="s" s="2">
         <v>101</v>
       </c>
       <c r="AJ60" t="s" s="2">
-        <v>119</v>
+        <v>102</v>
       </c>
       <c r="AK60" t="s" s="2">
         <v>79</v>
@@ -9693,10 +9688,10 @@
         <v>79</v>
       </c>
       <c r="AM60" t="s" s="2">
-        <v>79</v>
+        <v>290</v>
       </c>
       <c r="AN60" t="s" s="2">
-        <v>102</v>
+        <v>291</v>
       </c>
       <c r="AO60" t="s" s="2">
         <v>79</v>
@@ -9707,10 +9702,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -9718,7 +9713,7 @@
       </c>
       <c r="E61" s="2"/>
       <c r="F61" t="s" s="2">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="G61" t="s" s="2">
         <v>89</v>
@@ -9733,20 +9728,18 @@
         <v>90</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>133</v>
+        <v>105</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>286</v>
+        <v>294</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>287</v>
+        <v>295</v>
       </c>
       <c r="N61" t="s" s="2">
-        <v>288</v>
-      </c>
-      <c r="O61" t="s" s="2">
-        <v>289</v>
-      </c>
+        <v>296</v>
+      </c>
+      <c r="O61" s="2"/>
       <c r="P61" t="s" s="2">
         <v>79</v>
       </c>
@@ -9794,7 +9787,7 @@
         <v>79</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>291</v>
+        <v>297</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>77</v>
@@ -9806,7 +9799,7 @@
         <v>101</v>
       </c>
       <c r="AJ61" t="s" s="2">
-        <v>125</v>
+        <v>102</v>
       </c>
       <c r="AK61" t="s" s="2">
         <v>79</v>
@@ -9815,10 +9808,10 @@
         <v>79</v>
       </c>
       <c r="AM61" t="s" s="2">
-        <v>292</v>
+        <v>298</v>
       </c>
       <c r="AN61" t="s" s="2">
-        <v>293</v>
+        <v>299</v>
       </c>
       <c r="AO61" t="s" s="2">
         <v>79</v>
@@ -9829,10 +9822,10 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -9840,7 +9833,7 @@
       </c>
       <c r="E62" s="2"/>
       <c r="F62" t="s" s="2">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="G62" t="s" s="2">
         <v>89</v>
@@ -9855,18 +9848,20 @@
         <v>90</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>104</v>
+        <v>168</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>296</v>
+        <v>302</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>297</v>
+        <v>303</v>
       </c>
       <c r="N62" t="s" s="2">
-        <v>298</v>
-      </c>
-      <c r="O62" s="2"/>
+        <v>304</v>
+      </c>
+      <c r="O62" t="s" s="2">
+        <v>305</v>
+      </c>
       <c r="P62" t="s" s="2">
         <v>79</v>
       </c>
@@ -9914,7 +9909,7 @@
         <v>79</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>299</v>
+        <v>307</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>77</v>
@@ -9926,7 +9921,7 @@
         <v>101</v>
       </c>
       <c r="AJ62" t="s" s="2">
-        <v>125</v>
+        <v>102</v>
       </c>
       <c r="AK62" t="s" s="2">
         <v>79</v>
@@ -9935,10 +9930,10 @@
         <v>79</v>
       </c>
       <c r="AM62" t="s" s="2">
-        <v>300</v>
+        <v>308</v>
       </c>
       <c r="AN62" t="s" s="2">
-        <v>301</v>
+        <v>309</v>
       </c>
       <c r="AO62" t="s" s="2">
         <v>79</v>
@@ -9949,10 +9944,10 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -9960,7 +9955,7 @@
       </c>
       <c r="E63" s="2"/>
       <c r="F63" t="s" s="2">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="G63" t="s" s="2">
         <v>89</v>
@@ -9975,19 +9970,19 @@
         <v>90</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>170</v>
+        <v>105</v>
       </c>
       <c r="L63" t="s" s="2">
+        <v>312</v>
+      </c>
+      <c r="M63" t="s" s="2">
+        <v>313</v>
+      </c>
+      <c r="N63" t="s" s="2">
         <v>304</v>
       </c>
-      <c r="M63" t="s" s="2">
-        <v>305</v>
-      </c>
-      <c r="N63" t="s" s="2">
-        <v>306</v>
-      </c>
       <c r="O63" t="s" s="2">
-        <v>307</v>
+        <v>314</v>
       </c>
       <c r="P63" t="s" s="2">
         <v>79</v>
@@ -10036,7 +10031,7 @@
         <v>79</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>309</v>
+        <v>316</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>77</v>
@@ -10048,7 +10043,7 @@
         <v>101</v>
       </c>
       <c r="AJ63" t="s" s="2">
-        <v>125</v>
+        <v>102</v>
       </c>
       <c r="AK63" t="s" s="2">
         <v>79</v>
@@ -10057,10 +10052,10 @@
         <v>79</v>
       </c>
       <c r="AM63" t="s" s="2">
-        <v>310</v>
+        <v>317</v>
       </c>
       <c r="AN63" t="s" s="2">
-        <v>311</v>
+        <v>318</v>
       </c>
       <c r="AO63" t="s" s="2">
         <v>79</v>
@@ -10071,10 +10066,10 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -10097,19 +10092,19 @@
         <v>90</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>104</v>
+        <v>321</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>314</v>
+        <v>322</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>315</v>
+        <v>323</v>
       </c>
       <c r="N64" t="s" s="2">
-        <v>306</v>
+        <v>324</v>
       </c>
       <c r="O64" t="s" s="2">
-        <v>316</v>
+        <v>325</v>
       </c>
       <c r="P64" t="s" s="2">
         <v>79</v>
@@ -10158,7 +10153,7 @@
         <v>79</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>318</v>
+        <v>326</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>77</v>
@@ -10170,7 +10165,7 @@
         <v>101</v>
       </c>
       <c r="AJ64" t="s" s="2">
-        <v>125</v>
+        <v>102</v>
       </c>
       <c r="AK64" t="s" s="2">
         <v>79</v>
@@ -10179,10 +10174,10 @@
         <v>79</v>
       </c>
       <c r="AM64" t="s" s="2">
-        <v>319</v>
+        <v>327</v>
       </c>
       <c r="AN64" t="s" s="2">
-        <v>320</v>
+        <v>328</v>
       </c>
       <c r="AO64" t="s" s="2">
         <v>79</v>
@@ -10193,10 +10188,10 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -10219,19 +10214,19 @@
         <v>90</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>323</v>
+        <v>105</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>324</v>
+        <v>331</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>325</v>
+        <v>332</v>
       </c>
       <c r="N65" t="s" s="2">
-        <v>326</v>
+        <v>333</v>
       </c>
       <c r="O65" t="s" s="2">
-        <v>327</v>
+        <v>334</v>
       </c>
       <c r="P65" t="s" s="2">
         <v>79</v>
@@ -10280,7 +10275,7 @@
         <v>79</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>328</v>
+        <v>335</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>77</v>
@@ -10292,7 +10287,7 @@
         <v>101</v>
       </c>
       <c r="AJ65" t="s" s="2">
-        <v>125</v>
+        <v>102</v>
       </c>
       <c r="AK65" t="s" s="2">
         <v>79</v>
@@ -10301,10 +10296,10 @@
         <v>79</v>
       </c>
       <c r="AM65" t="s" s="2">
-        <v>329</v>
+        <v>336</v>
       </c>
       <c r="AN65" t="s" s="2">
-        <v>330</v>
+        <v>337</v>
       </c>
       <c r="AO65" t="s" s="2">
         <v>79</v>
@@ -10315,21 +10310,21 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
-        <v>79</v>
+        <v>496</v>
       </c>
       <c r="E66" s="2"/>
       <c r="F66" t="s" s="2">
         <v>77</v>
       </c>
       <c r="G66" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="H66" t="s" s="2">
         <v>79</v>
@@ -10338,22 +10333,22 @@
         <v>79</v>
       </c>
       <c r="J66" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>104</v>
+        <v>252</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>333</v>
+        <v>497</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>334</v>
+        <v>498</v>
       </c>
       <c r="N66" t="s" s="2">
-        <v>335</v>
+        <v>499</v>
       </c>
       <c r="O66" t="s" s="2">
-        <v>336</v>
+        <v>500</v>
       </c>
       <c r="P66" t="s" s="2">
         <v>79</v>
@@ -10378,13 +10373,13 @@
         <v>79</v>
       </c>
       <c r="X66" t="s" s="2">
-        <v>79</v>
+        <v>148</v>
       </c>
       <c r="Y66" t="s" s="2">
-        <v>79</v>
+        <v>501</v>
       </c>
       <c r="Z66" t="s" s="2">
-        <v>79</v>
+        <v>502</v>
       </c>
       <c r="AA66" t="s" s="2">
         <v>79</v>
@@ -10402,49 +10397,49 @@
         <v>79</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>337</v>
+        <v>495</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH66" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="AI66" t="s" s="2">
         <v>101</v>
       </c>
       <c r="AJ66" t="s" s="2">
-        <v>125</v>
+        <v>102</v>
       </c>
       <c r="AK66" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL66" t="s" s="2">
-        <v>79</v>
+        <v>503</v>
       </c>
       <c r="AM66" t="s" s="2">
-        <v>338</v>
+        <v>504</v>
       </c>
       <c r="AN66" t="s" s="2">
-        <v>339</v>
+        <v>505</v>
       </c>
       <c r="AO66" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AP66" t="s" s="2">
-        <v>79</v>
+        <v>506</v>
       </c>
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>497</v>
+        <v>507</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>497</v>
+        <v>507</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
-        <v>498</v>
+        <v>79</v>
       </c>
       <c r="E67" s="2"/>
       <c r="F67" t="s" s="2">
@@ -10463,19 +10458,19 @@
         <v>79</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>254</v>
+        <v>508</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>499</v>
+        <v>509</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>500</v>
+        <v>510</v>
       </c>
       <c r="N67" t="s" s="2">
-        <v>501</v>
+        <v>511</v>
       </c>
       <c r="O67" t="s" s="2">
-        <v>502</v>
+        <v>512</v>
       </c>
       <c r="P67" t="s" s="2">
         <v>79</v>
@@ -10500,13 +10495,13 @@
         <v>79</v>
       </c>
       <c r="X67" t="s" s="2">
-        <v>150</v>
+        <v>79</v>
       </c>
       <c r="Y67" t="s" s="2">
-        <v>503</v>
+        <v>79</v>
       </c>
       <c r="Z67" t="s" s="2">
-        <v>504</v>
+        <v>79</v>
       </c>
       <c r="AA67" t="s" s="2">
         <v>79</v>
@@ -10524,7 +10519,7 @@
         <v>79</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>497</v>
+        <v>507</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>77</v>
@@ -10536,33 +10531,33 @@
         <v>101</v>
       </c>
       <c r="AJ67" t="s" s="2">
-        <v>125</v>
+        <v>102</v>
       </c>
       <c r="AK67" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL67" t="s" s="2">
-        <v>505</v>
+        <v>79</v>
       </c>
       <c r="AM67" t="s" s="2">
-        <v>506</v>
+        <v>513</v>
       </c>
       <c r="AN67" t="s" s="2">
-        <v>507</v>
+        <v>514</v>
       </c>
       <c r="AO67" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AP67" t="s" s="2">
-        <v>508</v>
+        <v>79</v>
       </c>
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>509</v>
+        <v>515</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>509</v>
+        <v>515</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -10573,7 +10568,7 @@
         <v>77</v>
       </c>
       <c r="G68" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="H68" t="s" s="2">
         <v>79</v>
@@ -10585,20 +10580,18 @@
         <v>79</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>510</v>
+        <v>252</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>511</v>
+        <v>516</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>512</v>
+        <v>516</v>
       </c>
       <c r="N68" t="s" s="2">
-        <v>513</v>
-      </c>
-      <c r="O68" t="s" s="2">
-        <v>514</v>
-      </c>
+        <v>517</v>
+      </c>
+      <c r="O68" s="2"/>
       <c r="P68" t="s" s="2">
         <v>79</v>
       </c>
@@ -10622,13 +10615,13 @@
         <v>79</v>
       </c>
       <c r="X68" t="s" s="2">
-        <v>79</v>
+        <v>158</v>
       </c>
       <c r="Y68" t="s" s="2">
-        <v>79</v>
+        <v>518</v>
       </c>
       <c r="Z68" t="s" s="2">
-        <v>79</v>
+        <v>519</v>
       </c>
       <c r="AA68" t="s" s="2">
         <v>79</v>
@@ -10646,45 +10639,45 @@
         <v>79</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>509</v>
+        <v>515</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH68" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="AI68" t="s" s="2">
         <v>101</v>
       </c>
       <c r="AJ68" t="s" s="2">
-        <v>125</v>
+        <v>102</v>
       </c>
       <c r="AK68" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL68" t="s" s="2">
-        <v>79</v>
+        <v>520</v>
       </c>
       <c r="AM68" t="s" s="2">
-        <v>515</v>
+        <v>521</v>
       </c>
       <c r="AN68" t="s" s="2">
-        <v>516</v>
+        <v>522</v>
       </c>
       <c r="AO68" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AP68" t="s" s="2">
-        <v>79</v>
+        <v>523</v>
       </c>
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>517</v>
+        <v>524</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>517</v>
+        <v>524</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -10707,18 +10700,20 @@
         <v>79</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>518</v>
+        <v>525</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>518</v>
+        <v>526</v>
       </c>
       <c r="N69" t="s" s="2">
-        <v>519</v>
-      </c>
-      <c r="O69" s="2"/>
+        <v>527</v>
+      </c>
+      <c r="O69" t="s" s="2">
+        <v>528</v>
+      </c>
       <c r="P69" t="s" s="2">
         <v>79</v>
       </c>
@@ -10742,13 +10737,13 @@
         <v>79</v>
       </c>
       <c r="X69" t="s" s="2">
-        <v>160</v>
+        <v>243</v>
       </c>
       <c r="Y69" t="s" s="2">
-        <v>520</v>
+        <v>529</v>
       </c>
       <c r="Z69" t="s" s="2">
-        <v>521</v>
+        <v>529</v>
       </c>
       <c r="AA69" t="s" s="2">
         <v>79</v>
@@ -10766,7 +10761,7 @@
         <v>79</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>517</v>
+        <v>524</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>77</v>
@@ -10778,33 +10773,33 @@
         <v>101</v>
       </c>
       <c r="AJ69" t="s" s="2">
-        <v>125</v>
+        <v>102</v>
       </c>
       <c r="AK69" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL69" t="s" s="2">
-        <v>522</v>
+        <v>79</v>
       </c>
       <c r="AM69" t="s" s="2">
-        <v>523</v>
+        <v>530</v>
       </c>
       <c r="AN69" t="s" s="2">
-        <v>524</v>
+        <v>531</v>
       </c>
       <c r="AO69" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AP69" t="s" s="2">
-        <v>525</v>
+        <v>79</v>
       </c>
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>526</v>
+        <v>532</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>526</v>
+        <v>532</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -10827,20 +10822,16 @@
         <v>79</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>254</v>
+        <v>105</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>527</v>
+        <v>106</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>528</v>
-      </c>
-      <c r="N70" t="s" s="2">
-        <v>529</v>
-      </c>
-      <c r="O70" t="s" s="2">
-        <v>530</v>
-      </c>
+        <v>107</v>
+      </c>
+      <c r="N70" s="2"/>
+      <c r="O70" s="2"/>
       <c r="P70" t="s" s="2">
         <v>79</v>
       </c>
@@ -10864,13 +10855,13 @@
         <v>79</v>
       </c>
       <c r="X70" t="s" s="2">
-        <v>245</v>
+        <v>79</v>
       </c>
       <c r="Y70" t="s" s="2">
-        <v>531</v>
+        <v>79</v>
       </c>
       <c r="Z70" t="s" s="2">
-        <v>531</v>
+        <v>79</v>
       </c>
       <c r="AA70" t="s" s="2">
         <v>79</v>
@@ -10888,7 +10879,7 @@
         <v>79</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>526</v>
+        <v>108</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>77</v>
@@ -10897,10 +10888,10 @@
         <v>89</v>
       </c>
       <c r="AI70" t="s" s="2">
-        <v>101</v>
+        <v>79</v>
       </c>
       <c r="AJ70" t="s" s="2">
-        <v>125</v>
+        <v>79</v>
       </c>
       <c r="AK70" t="s" s="2">
         <v>79</v>
@@ -10909,10 +10900,10 @@
         <v>79</v>
       </c>
       <c r="AM70" t="s" s="2">
-        <v>532</v>
+        <v>79</v>
       </c>
       <c r="AN70" t="s" s="2">
-        <v>533</v>
+        <v>109</v>
       </c>
       <c r="AO70" t="s" s="2">
         <v>79</v>
@@ -10923,21 +10914,21 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
-        <v>79</v>
+        <v>111</v>
       </c>
       <c r="E71" s="2"/>
       <c r="F71" t="s" s="2">
         <v>77</v>
       </c>
       <c r="G71" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="H71" t="s" s="2">
         <v>79</v>
@@ -10949,15 +10940,17 @@
         <v>79</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>104</v>
+        <v>112</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>105</v>
+        <v>113</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>106</v>
-      </c>
-      <c r="N71" s="2"/>
+        <v>114</v>
+      </c>
+      <c r="N71" t="s" s="2">
+        <v>115</v>
+      </c>
       <c r="O71" s="2"/>
       <c r="P71" t="s" s="2">
         <v>79</v>
@@ -10994,31 +10987,31 @@
         <v>79</v>
       </c>
       <c r="AB71" t="s" s="2">
-        <v>79</v>
+        <v>116</v>
       </c>
       <c r="AC71" t="s" s="2">
-        <v>79</v>
+        <v>117</v>
       </c>
       <c r="AD71" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AE71" t="s" s="2">
-        <v>79</v>
+        <v>118</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>107</v>
+        <v>119</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH71" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="AI71" t="s" s="2">
-        <v>79</v>
+        <v>101</v>
       </c>
       <c r="AJ71" t="s" s="2">
-        <v>79</v>
+        <v>120</v>
       </c>
       <c r="AK71" t="s" s="2">
         <v>79</v>
@@ -11030,7 +11023,7 @@
         <v>79</v>
       </c>
       <c r="AN71" t="s" s="2">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="AO71" t="s" s="2">
         <v>79</v>
@@ -11041,14 +11034,14 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
-        <v>110</v>
+        <v>79</v>
       </c>
       <c r="E72" s="2"/>
       <c r="F72" t="s" s="2">
@@ -11064,21 +11057,23 @@
         <v>79</v>
       </c>
       <c r="J72" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>111</v>
+        <v>144</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>112</v>
+        <v>271</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>113</v>
+        <v>272</v>
       </c>
       <c r="N72" t="s" s="2">
-        <v>114</v>
-      </c>
-      <c r="O72" s="2"/>
+        <v>273</v>
+      </c>
+      <c r="O72" t="s" s="2">
+        <v>274</v>
+      </c>
       <c r="P72" t="s" s="2">
         <v>79</v>
       </c>
@@ -11114,19 +11109,19 @@
         <v>79</v>
       </c>
       <c r="AB72" t="s" s="2">
-        <v>115</v>
+        <v>79</v>
       </c>
       <c r="AC72" t="s" s="2">
-        <v>116</v>
+        <v>79</v>
       </c>
       <c r="AD72" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AE72" t="s" s="2">
-        <v>117</v>
+        <v>79</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>118</v>
+        <v>275</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>77</v>
@@ -11138,7 +11133,7 @@
         <v>101</v>
       </c>
       <c r="AJ72" t="s" s="2">
-        <v>119</v>
+        <v>102</v>
       </c>
       <c r="AK72" t="s" s="2">
         <v>79</v>
@@ -11147,10 +11142,10 @@
         <v>79</v>
       </c>
       <c r="AM72" t="s" s="2">
-        <v>79</v>
+        <v>276</v>
       </c>
       <c r="AN72" t="s" s="2">
-        <v>102</v>
+        <v>277</v>
       </c>
       <c r="AO72" t="s" s="2">
         <v>79</v>
@@ -11161,10 +11156,10 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -11175,7 +11170,7 @@
         <v>77</v>
       </c>
       <c r="G73" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="H73" t="s" s="2">
         <v>79</v>
@@ -11184,23 +11179,19 @@
         <v>79</v>
       </c>
       <c r="J73" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>146</v>
+        <v>105</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>273</v>
+        <v>106</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>274</v>
-      </c>
-      <c r="N73" t="s" s="2">
-        <v>275</v>
-      </c>
-      <c r="O73" t="s" s="2">
-        <v>276</v>
-      </c>
+        <v>107</v>
+      </c>
+      <c r="N73" s="2"/>
+      <c r="O73" s="2"/>
       <c r="P73" t="s" s="2">
         <v>79</v>
       </c>
@@ -11248,19 +11239,19 @@
         <v>79</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>277</v>
+        <v>108</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH73" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="AI73" t="s" s="2">
-        <v>101</v>
+        <v>79</v>
       </c>
       <c r="AJ73" t="s" s="2">
-        <v>125</v>
+        <v>79</v>
       </c>
       <c r="AK73" t="s" s="2">
         <v>79</v>
@@ -11269,10 +11260,10 @@
         <v>79</v>
       </c>
       <c r="AM73" t="s" s="2">
-        <v>278</v>
+        <v>79</v>
       </c>
       <c r="AN73" t="s" s="2">
-        <v>279</v>
+        <v>109</v>
       </c>
       <c r="AO73" t="s" s="2">
         <v>79</v>
@@ -11283,21 +11274,21 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
-        <v>79</v>
+        <v>111</v>
       </c>
       <c r="E74" s="2"/>
       <c r="F74" t="s" s="2">
         <v>77</v>
       </c>
       <c r="G74" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="H74" t="s" s="2">
         <v>79</v>
@@ -11309,15 +11300,17 @@
         <v>79</v>
       </c>
       <c r="K74" t="s" s="2">
-        <v>104</v>
+        <v>112</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>105</v>
+        <v>113</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>106</v>
-      </c>
-      <c r="N74" s="2"/>
+        <v>114</v>
+      </c>
+      <c r="N74" t="s" s="2">
+        <v>115</v>
+      </c>
       <c r="O74" s="2"/>
       <c r="P74" t="s" s="2">
         <v>79</v>
@@ -11354,31 +11347,31 @@
         <v>79</v>
       </c>
       <c r="AB74" t="s" s="2">
-        <v>79</v>
+        <v>116</v>
       </c>
       <c r="AC74" t="s" s="2">
-        <v>79</v>
+        <v>117</v>
       </c>
       <c r="AD74" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AE74" t="s" s="2">
-        <v>79</v>
+        <v>118</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>107</v>
+        <v>119</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH74" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="AI74" t="s" s="2">
-        <v>79</v>
+        <v>101</v>
       </c>
       <c r="AJ74" t="s" s="2">
-        <v>79</v>
+        <v>120</v>
       </c>
       <c r="AK74" t="s" s="2">
         <v>79</v>
@@ -11390,7 +11383,7 @@
         <v>79</v>
       </c>
       <c r="AN74" t="s" s="2">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="AO74" t="s" s="2">
         <v>79</v>
@@ -11401,21 +11394,21 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
-        <v>110</v>
+        <v>79</v>
       </c>
       <c r="E75" s="2"/>
       <c r="F75" t="s" s="2">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="G75" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="H75" t="s" s="2">
         <v>79</v>
@@ -11424,21 +11417,23 @@
         <v>79</v>
       </c>
       <c r="J75" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>111</v>
+        <v>133</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>112</v>
+        <v>284</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>113</v>
+        <v>285</v>
       </c>
       <c r="N75" t="s" s="2">
-        <v>114</v>
-      </c>
-      <c r="O75" s="2"/>
+        <v>286</v>
+      </c>
+      <c r="O75" t="s" s="2">
+        <v>287</v>
+      </c>
       <c r="P75" t="s" s="2">
         <v>79</v>
       </c>
@@ -11474,31 +11469,31 @@
         <v>79</v>
       </c>
       <c r="AB75" t="s" s="2">
-        <v>115</v>
+        <v>79</v>
       </c>
       <c r="AC75" t="s" s="2">
-        <v>116</v>
+        <v>79</v>
       </c>
       <c r="AD75" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AE75" t="s" s="2">
-        <v>117</v>
+        <v>79</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>118</v>
+        <v>289</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH75" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="AI75" t="s" s="2">
         <v>101</v>
       </c>
       <c r="AJ75" t="s" s="2">
-        <v>119</v>
+        <v>102</v>
       </c>
       <c r="AK75" t="s" s="2">
         <v>79</v>
@@ -11507,10 +11502,10 @@
         <v>79</v>
       </c>
       <c r="AM75" t="s" s="2">
-        <v>79</v>
+        <v>290</v>
       </c>
       <c r="AN75" t="s" s="2">
-        <v>102</v>
+        <v>291</v>
       </c>
       <c r="AO75" t="s" s="2">
         <v>79</v>
@@ -11521,10 +11516,10 @@
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -11532,7 +11527,7 @@
       </c>
       <c r="E76" s="2"/>
       <c r="F76" t="s" s="2">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="G76" t="s" s="2">
         <v>89</v>
@@ -11547,20 +11542,18 @@
         <v>90</v>
       </c>
       <c r="K76" t="s" s="2">
-        <v>133</v>
+        <v>105</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>286</v>
+        <v>294</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>287</v>
+        <v>295</v>
       </c>
       <c r="N76" t="s" s="2">
-        <v>288</v>
-      </c>
-      <c r="O76" t="s" s="2">
-        <v>289</v>
-      </c>
+        <v>296</v>
+      </c>
+      <c r="O76" s="2"/>
       <c r="P76" t="s" s="2">
         <v>79</v>
       </c>
@@ -11608,7 +11601,7 @@
         <v>79</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>291</v>
+        <v>297</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>77</v>
@@ -11620,7 +11613,7 @@
         <v>101</v>
       </c>
       <c r="AJ76" t="s" s="2">
-        <v>125</v>
+        <v>102</v>
       </c>
       <c r="AK76" t="s" s="2">
         <v>79</v>
@@ -11629,10 +11622,10 @@
         <v>79</v>
       </c>
       <c r="AM76" t="s" s="2">
-        <v>292</v>
+        <v>298</v>
       </c>
       <c r="AN76" t="s" s="2">
-        <v>293</v>
+        <v>299</v>
       </c>
       <c r="AO76" t="s" s="2">
         <v>79</v>
@@ -11643,10 +11636,10 @@
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -11654,7 +11647,7 @@
       </c>
       <c r="E77" s="2"/>
       <c r="F77" t="s" s="2">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="G77" t="s" s="2">
         <v>89</v>
@@ -11669,18 +11662,20 @@
         <v>90</v>
       </c>
       <c r="K77" t="s" s="2">
-        <v>104</v>
+        <v>168</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>296</v>
+        <v>302</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>297</v>
+        <v>303</v>
       </c>
       <c r="N77" t="s" s="2">
-        <v>298</v>
-      </c>
-      <c r="O77" s="2"/>
+        <v>304</v>
+      </c>
+      <c r="O77" t="s" s="2">
+        <v>305</v>
+      </c>
       <c r="P77" t="s" s="2">
         <v>79</v>
       </c>
@@ -11728,7 +11723,7 @@
         <v>79</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>299</v>
+        <v>307</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>77</v>
@@ -11740,7 +11735,7 @@
         <v>101</v>
       </c>
       <c r="AJ77" t="s" s="2">
-        <v>125</v>
+        <v>102</v>
       </c>
       <c r="AK77" t="s" s="2">
         <v>79</v>
@@ -11749,10 +11744,10 @@
         <v>79</v>
       </c>
       <c r="AM77" t="s" s="2">
-        <v>300</v>
+        <v>308</v>
       </c>
       <c r="AN77" t="s" s="2">
-        <v>301</v>
+        <v>309</v>
       </c>
       <c r="AO77" t="s" s="2">
         <v>79</v>
@@ -11763,10 +11758,10 @@
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -11774,7 +11769,7 @@
       </c>
       <c r="E78" s="2"/>
       <c r="F78" t="s" s="2">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="G78" t="s" s="2">
         <v>89</v>
@@ -11789,19 +11784,19 @@
         <v>90</v>
       </c>
       <c r="K78" t="s" s="2">
-        <v>170</v>
+        <v>105</v>
       </c>
       <c r="L78" t="s" s="2">
+        <v>312</v>
+      </c>
+      <c r="M78" t="s" s="2">
+        <v>313</v>
+      </c>
+      <c r="N78" t="s" s="2">
         <v>304</v>
       </c>
-      <c r="M78" t="s" s="2">
-        <v>305</v>
-      </c>
-      <c r="N78" t="s" s="2">
-        <v>306</v>
-      </c>
       <c r="O78" t="s" s="2">
-        <v>307</v>
+        <v>314</v>
       </c>
       <c r="P78" t="s" s="2">
         <v>79</v>
@@ -11850,7 +11845,7 @@
         <v>79</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>309</v>
+        <v>316</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>77</v>
@@ -11862,7 +11857,7 @@
         <v>101</v>
       </c>
       <c r="AJ78" t="s" s="2">
-        <v>125</v>
+        <v>102</v>
       </c>
       <c r="AK78" t="s" s="2">
         <v>79</v>
@@ -11871,10 +11866,10 @@
         <v>79</v>
       </c>
       <c r="AM78" t="s" s="2">
-        <v>310</v>
+        <v>317</v>
       </c>
       <c r="AN78" t="s" s="2">
-        <v>311</v>
+        <v>318</v>
       </c>
       <c r="AO78" t="s" s="2">
         <v>79</v>
@@ -11885,10 +11880,10 @@
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -11911,19 +11906,19 @@
         <v>90</v>
       </c>
       <c r="K79" t="s" s="2">
-        <v>104</v>
+        <v>321</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>314</v>
+        <v>322</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>315</v>
+        <v>323</v>
       </c>
       <c r="N79" t="s" s="2">
-        <v>306</v>
+        <v>324</v>
       </c>
       <c r="O79" t="s" s="2">
-        <v>316</v>
+        <v>325</v>
       </c>
       <c r="P79" t="s" s="2">
         <v>79</v>
@@ -11972,7 +11967,7 @@
         <v>79</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>318</v>
+        <v>326</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>77</v>
@@ -11984,7 +11979,7 @@
         <v>101</v>
       </c>
       <c r="AJ79" t="s" s="2">
-        <v>125</v>
+        <v>102</v>
       </c>
       <c r="AK79" t="s" s="2">
         <v>79</v>
@@ -11993,10 +11988,10 @@
         <v>79</v>
       </c>
       <c r="AM79" t="s" s="2">
-        <v>319</v>
+        <v>327</v>
       </c>
       <c r="AN79" t="s" s="2">
-        <v>320</v>
+        <v>328</v>
       </c>
       <c r="AO79" t="s" s="2">
         <v>79</v>
@@ -12007,10 +12002,10 @@
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -12033,19 +12028,19 @@
         <v>90</v>
       </c>
       <c r="K80" t="s" s="2">
-        <v>323</v>
+        <v>105</v>
       </c>
       <c r="L80" t="s" s="2">
-        <v>324</v>
+        <v>331</v>
       </c>
       <c r="M80" t="s" s="2">
-        <v>325</v>
+        <v>332</v>
       </c>
       <c r="N80" t="s" s="2">
-        <v>326</v>
+        <v>333</v>
       </c>
       <c r="O80" t="s" s="2">
-        <v>327</v>
+        <v>334</v>
       </c>
       <c r="P80" t="s" s="2">
         <v>79</v>
@@ -12094,7 +12089,7 @@
         <v>79</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>328</v>
+        <v>335</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>77</v>
@@ -12106,7 +12101,7 @@
         <v>101</v>
       </c>
       <c r="AJ80" t="s" s="2">
-        <v>125</v>
+        <v>102</v>
       </c>
       <c r="AK80" t="s" s="2">
         <v>79</v>
@@ -12115,10 +12110,10 @@
         <v>79</v>
       </c>
       <c r="AM80" t="s" s="2">
-        <v>329</v>
+        <v>336</v>
       </c>
       <c r="AN80" t="s" s="2">
-        <v>330</v>
+        <v>337</v>
       </c>
       <c r="AO80" t="s" s="2">
         <v>79</v>
@@ -12129,10 +12124,10 @@
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -12152,23 +12147,21 @@
         <v>79</v>
       </c>
       <c r="J81" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="K81" t="s" s="2">
-        <v>104</v>
+        <v>544</v>
       </c>
       <c r="L81" t="s" s="2">
-        <v>333</v>
+        <v>545</v>
       </c>
       <c r="M81" t="s" s="2">
-        <v>334</v>
+        <v>546</v>
       </c>
       <c r="N81" t="s" s="2">
-        <v>335</v>
-      </c>
-      <c r="O81" t="s" s="2">
-        <v>336</v>
-      </c>
+        <v>547</v>
+      </c>
+      <c r="O81" s="2"/>
       <c r="P81" t="s" s="2">
         <v>79</v>
       </c>
@@ -12216,7 +12209,7 @@
         <v>79</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>337</v>
+        <v>543</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>77</v>
@@ -12228,33 +12221,33 @@
         <v>101</v>
       </c>
       <c r="AJ81" t="s" s="2">
-        <v>125</v>
+        <v>225</v>
       </c>
       <c r="AK81" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL81" t="s" s="2">
-        <v>79</v>
+        <v>548</v>
       </c>
       <c r="AM81" t="s" s="2">
-        <v>338</v>
+        <v>549</v>
       </c>
       <c r="AN81" t="s" s="2">
-        <v>339</v>
+        <v>550</v>
       </c>
       <c r="AO81" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AP81" t="s" s="2">
-        <v>79</v>
+        <v>551</v>
       </c>
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>545</v>
+        <v>552</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>545</v>
+        <v>552</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -12277,16 +12270,16 @@
         <v>79</v>
       </c>
       <c r="K82" t="s" s="2">
-        <v>546</v>
+        <v>553</v>
       </c>
       <c r="L82" t="s" s="2">
-        <v>547</v>
+        <v>554</v>
       </c>
       <c r="M82" t="s" s="2">
-        <v>548</v>
+        <v>555</v>
       </c>
       <c r="N82" t="s" s="2">
-        <v>549</v>
+        <v>556</v>
       </c>
       <c r="O82" s="2"/>
       <c r="P82" t="s" s="2">
@@ -12336,7 +12329,7 @@
         <v>79</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>545</v>
+        <v>552</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>77</v>
@@ -12348,33 +12341,33 @@
         <v>101</v>
       </c>
       <c r="AJ82" t="s" s="2">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="AK82" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL82" t="s" s="2">
-        <v>550</v>
+        <v>557</v>
       </c>
       <c r="AM82" t="s" s="2">
-        <v>551</v>
+        <v>558</v>
       </c>
       <c r="AN82" t="s" s="2">
-        <v>552</v>
+        <v>559</v>
       </c>
       <c r="AO82" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AP82" t="s" s="2">
-        <v>553</v>
+        <v>560</v>
       </c>
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>554</v>
+        <v>561</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>554</v>
+        <v>561</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -12385,7 +12378,7 @@
         <v>77</v>
       </c>
       <c r="G83" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="H83" t="s" s="2">
         <v>79</v>
@@ -12397,18 +12390,20 @@
         <v>79</v>
       </c>
       <c r="K83" t="s" s="2">
-        <v>555</v>
+        <v>562</v>
       </c>
       <c r="L83" t="s" s="2">
-        <v>556</v>
+        <v>563</v>
       </c>
       <c r="M83" t="s" s="2">
-        <v>557</v>
+        <v>564</v>
       </c>
       <c r="N83" t="s" s="2">
-        <v>558</v>
-      </c>
-      <c r="O83" s="2"/>
+        <v>565</v>
+      </c>
+      <c r="O83" t="s" s="2">
+        <v>566</v>
+      </c>
       <c r="P83" t="s" s="2">
         <v>79</v>
       </c>
@@ -12456,45 +12451,45 @@
         <v>79</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>554</v>
+        <v>561</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH83" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="AI83" t="s" s="2">
         <v>101</v>
       </c>
       <c r="AJ83" t="s" s="2">
-        <v>227</v>
+        <v>567</v>
       </c>
       <c r="AK83" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL83" t="s" s="2">
-        <v>559</v>
+        <v>79</v>
       </c>
       <c r="AM83" t="s" s="2">
-        <v>560</v>
+        <v>568</v>
       </c>
       <c r="AN83" t="s" s="2">
-        <v>561</v>
+        <v>569</v>
       </c>
       <c r="AO83" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AP83" t="s" s="2">
-        <v>562</v>
+        <v>79</v>
       </c>
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>563</v>
+        <v>570</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>563</v>
+        <v>570</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -12505,7 +12500,7 @@
         <v>77</v>
       </c>
       <c r="G84" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="H84" t="s" s="2">
         <v>79</v>
@@ -12517,20 +12512,16 @@
         <v>79</v>
       </c>
       <c r="K84" t="s" s="2">
-        <v>564</v>
+        <v>105</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>565</v>
+        <v>106</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>566</v>
-      </c>
-      <c r="N84" t="s" s="2">
-        <v>567</v>
-      </c>
-      <c r="O84" t="s" s="2">
-        <v>568</v>
-      </c>
+        <v>107</v>
+      </c>
+      <c r="N84" s="2"/>
+      <c r="O84" s="2"/>
       <c r="P84" t="s" s="2">
         <v>79</v>
       </c>
@@ -12578,19 +12569,19 @@
         <v>79</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>563</v>
+        <v>108</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH84" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="AI84" t="s" s="2">
-        <v>101</v>
+        <v>79</v>
       </c>
       <c r="AJ84" t="s" s="2">
-        <v>569</v>
+        <v>79</v>
       </c>
       <c r="AK84" t="s" s="2">
         <v>79</v>
@@ -12599,10 +12590,10 @@
         <v>79</v>
       </c>
       <c r="AM84" t="s" s="2">
-        <v>570</v>
+        <v>79</v>
       </c>
       <c r="AN84" t="s" s="2">
-        <v>571</v>
+        <v>109</v>
       </c>
       <c r="AO84" t="s" s="2">
         <v>79</v>
@@ -12613,21 +12604,21 @@
     </row>
     <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
-        <v>79</v>
+        <v>111</v>
       </c>
       <c r="E85" s="2"/>
       <c r="F85" t="s" s="2">
         <v>77</v>
       </c>
       <c r="G85" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="H85" t="s" s="2">
         <v>79</v>
@@ -12639,15 +12630,17 @@
         <v>79</v>
       </c>
       <c r="K85" t="s" s="2">
-        <v>104</v>
+        <v>112</v>
       </c>
       <c r="L85" t="s" s="2">
-        <v>105</v>
+        <v>113</v>
       </c>
       <c r="M85" t="s" s="2">
-        <v>106</v>
-      </c>
-      <c r="N85" s="2"/>
+        <v>114</v>
+      </c>
+      <c r="N85" t="s" s="2">
+        <v>115</v>
+      </c>
       <c r="O85" s="2"/>
       <c r="P85" t="s" s="2">
         <v>79</v>
@@ -12684,31 +12677,31 @@
         <v>79</v>
       </c>
       <c r="AB85" t="s" s="2">
-        <v>79</v>
+        <v>116</v>
       </c>
       <c r="AC85" t="s" s="2">
-        <v>79</v>
+        <v>117</v>
       </c>
       <c r="AD85" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AE85" t="s" s="2">
-        <v>79</v>
+        <v>118</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>107</v>
+        <v>119</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH85" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="AI85" t="s" s="2">
-        <v>79</v>
+        <v>101</v>
       </c>
       <c r="AJ85" t="s" s="2">
-        <v>79</v>
+        <v>120</v>
       </c>
       <c r="AK85" t="s" s="2">
         <v>79</v>
@@ -12720,7 +12713,7 @@
         <v>79</v>
       </c>
       <c r="AN85" t="s" s="2">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="AO85" t="s" s="2">
         <v>79</v>
@@ -12731,14 +12724,14 @@
     </row>
     <row r="86" hidden="true">
       <c r="A86" t="s" s="2">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
-        <v>110</v>
+        <v>573</v>
       </c>
       <c r="E86" s="2"/>
       <c r="F86" t="s" s="2">
@@ -12751,24 +12744,26 @@
         <v>79</v>
       </c>
       <c r="I86" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="J86" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="K86" t="s" s="2">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="L86" t="s" s="2">
-        <v>112</v>
+        <v>574</v>
       </c>
       <c r="M86" t="s" s="2">
-        <v>113</v>
+        <v>575</v>
       </c>
       <c r="N86" t="s" s="2">
-        <v>114</v>
-      </c>
-      <c r="O86" s="2"/>
+        <v>115</v>
+      </c>
+      <c r="O86" t="s" s="2">
+        <v>207</v>
+      </c>
       <c r="P86" t="s" s="2">
         <v>79</v>
       </c>
@@ -12804,19 +12799,19 @@
         <v>79</v>
       </c>
       <c r="AB86" t="s" s="2">
-        <v>115</v>
+        <v>79</v>
       </c>
       <c r="AC86" t="s" s="2">
-        <v>116</v>
+        <v>79</v>
       </c>
       <c r="AD86" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AE86" t="s" s="2">
-        <v>117</v>
+        <v>79</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>118</v>
+        <v>576</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>77</v>
@@ -12828,7 +12823,7 @@
         <v>101</v>
       </c>
       <c r="AJ86" t="s" s="2">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="AK86" t="s" s="2">
         <v>79</v>
@@ -12840,7 +12835,7 @@
         <v>79</v>
       </c>
       <c r="AN86" t="s" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="AO86" t="s" s="2">
         <v>79</v>
@@ -12851,46 +12846,44 @@
     </row>
     <row r="87" hidden="true">
       <c r="A87" t="s" s="2">
-        <v>574</v>
+        <v>577</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>574</v>
+        <v>577</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
-        <v>575</v>
+        <v>79</v>
       </c>
       <c r="E87" s="2"/>
       <c r="F87" t="s" s="2">
         <v>77</v>
       </c>
       <c r="G87" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="H87" t="s" s="2">
         <v>79</v>
       </c>
       <c r="I87" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="J87" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="K87" t="s" s="2">
-        <v>111</v>
+        <v>578</v>
       </c>
       <c r="L87" t="s" s="2">
-        <v>576</v>
+        <v>579</v>
       </c>
       <c r="M87" t="s" s="2">
-        <v>577</v>
+        <v>580</v>
       </c>
       <c r="N87" t="s" s="2">
-        <v>114</v>
-      </c>
-      <c r="O87" t="s" s="2">
-        <v>209</v>
-      </c>
+        <v>581</v>
+      </c>
+      <c r="O87" s="2"/>
       <c r="P87" t="s" s="2">
         <v>79</v>
       </c>
@@ -12938,19 +12931,19 @@
         <v>79</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH87" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="AI87" t="s" s="2">
-        <v>101</v>
+        <v>582</v>
       </c>
       <c r="AJ87" t="s" s="2">
-        <v>119</v>
+        <v>583</v>
       </c>
       <c r="AK87" t="s" s="2">
         <v>79</v>
@@ -12959,10 +12952,10 @@
         <v>79</v>
       </c>
       <c r="AM87" t="s" s="2">
-        <v>79</v>
+        <v>584</v>
       </c>
       <c r="AN87" t="s" s="2">
-        <v>102</v>
+        <v>585</v>
       </c>
       <c r="AO87" t="s" s="2">
         <v>79</v>
@@ -12973,10 +12966,10 @@
     </row>
     <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
-        <v>579</v>
+        <v>586</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>579</v>
+        <v>586</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -12999,16 +12992,16 @@
         <v>79</v>
       </c>
       <c r="K88" t="s" s="2">
-        <v>580</v>
+        <v>578</v>
       </c>
       <c r="L88" t="s" s="2">
+        <v>587</v>
+      </c>
+      <c r="M88" t="s" s="2">
+        <v>588</v>
+      </c>
+      <c r="N88" t="s" s="2">
         <v>581</v>
-      </c>
-      <c r="M88" t="s" s="2">
-        <v>582</v>
-      </c>
-      <c r="N88" t="s" s="2">
-        <v>583</v>
       </c>
       <c r="O88" s="2"/>
       <c r="P88" t="s" s="2">
@@ -13058,7 +13051,7 @@
         <v>79</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>579</v>
+        <v>586</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>77</v>
@@ -13067,22 +13060,22 @@
         <v>89</v>
       </c>
       <c r="AI88" t="s" s="2">
+        <v>582</v>
+      </c>
+      <c r="AJ88" t="s" s="2">
+        <v>583</v>
+      </c>
+      <c r="AK88" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AL88" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AM88" t="s" s="2">
         <v>584</v>
       </c>
-      <c r="AJ88" t="s" s="2">
-        <v>585</v>
-      </c>
-      <c r="AK88" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AL88" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AM88" t="s" s="2">
-        <v>586</v>
-      </c>
       <c r="AN88" t="s" s="2">
-        <v>587</v>
+        <v>589</v>
       </c>
       <c r="AO88" t="s" s="2">
         <v>79</v>
@@ -13093,10 +13086,10 @@
     </row>
     <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
-        <v>588</v>
+        <v>590</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>588</v>
+        <v>590</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -13119,18 +13112,20 @@
         <v>79</v>
       </c>
       <c r="K89" t="s" s="2">
-        <v>580</v>
+        <v>252</v>
       </c>
       <c r="L89" t="s" s="2">
-        <v>589</v>
+        <v>591</v>
       </c>
       <c r="M89" t="s" s="2">
-        <v>590</v>
+        <v>592</v>
       </c>
       <c r="N89" t="s" s="2">
-        <v>583</v>
-      </c>
-      <c r="O89" s="2"/>
+        <v>593</v>
+      </c>
+      <c r="O89" t="s" s="2">
+        <v>594</v>
+      </c>
       <c r="P89" t="s" s="2">
         <v>79</v>
       </c>
@@ -13154,13 +13149,13 @@
         <v>79</v>
       </c>
       <c r="X89" t="s" s="2">
-        <v>79</v>
+        <v>172</v>
       </c>
       <c r="Y89" t="s" s="2">
-        <v>79</v>
+        <v>595</v>
       </c>
       <c r="Z89" t="s" s="2">
-        <v>79</v>
+        <v>596</v>
       </c>
       <c r="AA89" t="s" s="2">
         <v>79</v>
@@ -13178,7 +13173,7 @@
         <v>79</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>588</v>
+        <v>590</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>77</v>
@@ -13187,22 +13182,22 @@
         <v>89</v>
       </c>
       <c r="AI89" t="s" s="2">
-        <v>584</v>
+        <v>101</v>
       </c>
       <c r="AJ89" t="s" s="2">
-        <v>585</v>
+        <v>102</v>
       </c>
       <c r="AK89" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL89" t="s" s="2">
-        <v>79</v>
+        <v>597</v>
       </c>
       <c r="AM89" t="s" s="2">
-        <v>586</v>
+        <v>598</v>
       </c>
       <c r="AN89" t="s" s="2">
-        <v>591</v>
+        <v>505</v>
       </c>
       <c r="AO89" t="s" s="2">
         <v>79</v>
@@ -13213,10 +13208,10 @@
     </row>
     <row r="90" hidden="true">
       <c r="A90" t="s" s="2">
-        <v>592</v>
+        <v>599</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>592</v>
+        <v>599</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -13227,7 +13222,7 @@
         <v>77</v>
       </c>
       <c r="G90" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="H90" t="s" s="2">
         <v>79</v>
@@ -13239,19 +13234,19 @@
         <v>79</v>
       </c>
       <c r="K90" t="s" s="2">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="L90" t="s" s="2">
-        <v>593</v>
+        <v>600</v>
       </c>
       <c r="M90" t="s" s="2">
-        <v>594</v>
+        <v>601</v>
       </c>
       <c r="N90" t="s" s="2">
-        <v>595</v>
+        <v>602</v>
       </c>
       <c r="O90" t="s" s="2">
-        <v>596</v>
+        <v>603</v>
       </c>
       <c r="P90" t="s" s="2">
         <v>79</v>
@@ -13276,13 +13271,13 @@
         <v>79</v>
       </c>
       <c r="X90" t="s" s="2">
-        <v>174</v>
+        <v>158</v>
       </c>
       <c r="Y90" t="s" s="2">
-        <v>597</v>
+        <v>604</v>
       </c>
       <c r="Z90" t="s" s="2">
-        <v>598</v>
+        <v>605</v>
       </c>
       <c r="AA90" t="s" s="2">
         <v>79</v>
@@ -13300,31 +13295,31 @@
         <v>79</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>592</v>
+        <v>599</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH90" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="AI90" t="s" s="2">
         <v>101</v>
       </c>
       <c r="AJ90" t="s" s="2">
-        <v>125</v>
+        <v>102</v>
       </c>
       <c r="AK90" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL90" t="s" s="2">
-        <v>599</v>
+        <v>597</v>
       </c>
       <c r="AM90" t="s" s="2">
-        <v>600</v>
+        <v>598</v>
       </c>
       <c r="AN90" t="s" s="2">
-        <v>507</v>
+        <v>505</v>
       </c>
       <c r="AO90" t="s" s="2">
         <v>79</v>
@@ -13335,10 +13330,10 @@
     </row>
     <row r="91" hidden="true">
       <c r="A91" t="s" s="2">
-        <v>601</v>
+        <v>606</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>601</v>
+        <v>606</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -13349,7 +13344,7 @@
         <v>77</v>
       </c>
       <c r="G91" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="H91" t="s" s="2">
         <v>79</v>
@@ -13361,19 +13356,19 @@
         <v>79</v>
       </c>
       <c r="K91" t="s" s="2">
-        <v>254</v>
+        <v>607</v>
       </c>
       <c r="L91" t="s" s="2">
-        <v>602</v>
+        <v>608</v>
       </c>
       <c r="M91" t="s" s="2">
-        <v>603</v>
+        <v>609</v>
       </c>
       <c r="N91" t="s" s="2">
-        <v>604</v>
+        <v>610</v>
       </c>
       <c r="O91" t="s" s="2">
-        <v>605</v>
+        <v>611</v>
       </c>
       <c r="P91" t="s" s="2">
         <v>79</v>
@@ -13398,55 +13393,55 @@
         <v>79</v>
       </c>
       <c r="X91" t="s" s="2">
-        <v>160</v>
+        <v>79</v>
       </c>
       <c r="Y91" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Z91" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AA91" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AB91" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AC91" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AD91" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AE91" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AF91" t="s" s="2">
         <v>606</v>
       </c>
-      <c r="Z91" t="s" s="2">
-        <v>607</v>
-      </c>
-      <c r="AA91" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AB91" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC91" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AD91" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AE91" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AF91" t="s" s="2">
-        <v>601</v>
-      </c>
       <c r="AG91" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH91" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="AI91" t="s" s="2">
         <v>101</v>
       </c>
       <c r="AJ91" t="s" s="2">
-        <v>125</v>
+        <v>612</v>
       </c>
       <c r="AK91" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL91" t="s" s="2">
-        <v>599</v>
+        <v>79</v>
       </c>
       <c r="AM91" t="s" s="2">
-        <v>600</v>
+        <v>613</v>
       </c>
       <c r="AN91" t="s" s="2">
-        <v>507</v>
+        <v>614</v>
       </c>
       <c r="AO91" t="s" s="2">
         <v>79</v>
@@ -13457,10 +13452,10 @@
     </row>
     <row r="92" hidden="true">
       <c r="A92" t="s" s="2">
-        <v>608</v>
+        <v>615</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>608</v>
+        <v>615</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -13483,20 +13478,18 @@
         <v>79</v>
       </c>
       <c r="K92" t="s" s="2">
-        <v>609</v>
+        <v>105</v>
       </c>
       <c r="L92" t="s" s="2">
-        <v>610</v>
+        <v>616</v>
       </c>
       <c r="M92" t="s" s="2">
-        <v>611</v>
+        <v>617</v>
       </c>
       <c r="N92" t="s" s="2">
-        <v>612</v>
-      </c>
-      <c r="O92" t="s" s="2">
-        <v>613</v>
-      </c>
+        <v>304</v>
+      </c>
+      <c r="O92" s="2"/>
       <c r="P92" t="s" s="2">
         <v>79</v>
       </c>
@@ -13544,7 +13537,7 @@
         <v>79</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>608</v>
+        <v>615</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>77</v>
@@ -13556,7 +13549,7 @@
         <v>101</v>
       </c>
       <c r="AJ92" t="s" s="2">
-        <v>614</v>
+        <v>102</v>
       </c>
       <c r="AK92" t="s" s="2">
         <v>79</v>
@@ -13565,10 +13558,10 @@
         <v>79</v>
       </c>
       <c r="AM92" t="s" s="2">
-        <v>615</v>
+        <v>584</v>
       </c>
       <c r="AN92" t="s" s="2">
-        <v>616</v>
+        <v>618</v>
       </c>
       <c r="AO92" t="s" s="2">
         <v>79</v>
@@ -13579,10 +13572,10 @@
     </row>
     <row r="93" hidden="true">
       <c r="A93" t="s" s="2">
-        <v>617</v>
+        <v>619</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>617</v>
+        <v>619</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -13593,7 +13586,7 @@
         <v>77</v>
       </c>
       <c r="G93" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="H93" t="s" s="2">
         <v>79</v>
@@ -13602,19 +13595,19 @@
         <v>79</v>
       </c>
       <c r="J93" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="K93" t="s" s="2">
-        <v>104</v>
+        <v>620</v>
       </c>
       <c r="L93" t="s" s="2">
-        <v>618</v>
+        <v>621</v>
       </c>
       <c r="M93" t="s" s="2">
-        <v>619</v>
+        <v>622</v>
       </c>
       <c r="N93" t="s" s="2">
-        <v>306</v>
+        <v>623</v>
       </c>
       <c r="O93" s="2"/>
       <c r="P93" t="s" s="2">
@@ -13664,19 +13657,19 @@
         <v>79</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>617</v>
+        <v>619</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH93" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="AI93" t="s" s="2">
         <v>101</v>
       </c>
       <c r="AJ93" t="s" s="2">
-        <v>125</v>
+        <v>225</v>
       </c>
       <c r="AK93" t="s" s="2">
         <v>79</v>
@@ -13685,10 +13678,10 @@
         <v>79</v>
       </c>
       <c r="AM93" t="s" s="2">
-        <v>586</v>
+        <v>624</v>
       </c>
       <c r="AN93" t="s" s="2">
-        <v>620</v>
+        <v>625</v>
       </c>
       <c r="AO93" t="s" s="2">
         <v>79</v>
@@ -13699,10 +13692,10 @@
     </row>
     <row r="94" hidden="true">
       <c r="A94" t="s" s="2">
-        <v>621</v>
+        <v>626</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>621</v>
+        <v>626</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -13725,16 +13718,16 @@
         <v>90</v>
       </c>
       <c r="K94" t="s" s="2">
-        <v>622</v>
+        <v>627</v>
       </c>
       <c r="L94" t="s" s="2">
-        <v>623</v>
+        <v>628</v>
       </c>
       <c r="M94" t="s" s="2">
-        <v>624</v>
+        <v>629</v>
       </c>
       <c r="N94" t="s" s="2">
-        <v>625</v>
+        <v>630</v>
       </c>
       <c r="O94" s="2"/>
       <c r="P94" t="s" s="2">
@@ -13784,7 +13777,7 @@
         <v>79</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>621</v>
+        <v>626</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>77</v>
@@ -13796,7 +13789,7 @@
         <v>101</v>
       </c>
       <c r="AJ94" t="s" s="2">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="AK94" t="s" s="2">
         <v>79</v>
@@ -13805,10 +13798,10 @@
         <v>79</v>
       </c>
       <c r="AM94" t="s" s="2">
-        <v>626</v>
+        <v>624</v>
       </c>
       <c r="AN94" t="s" s="2">
-        <v>627</v>
+        <v>631</v>
       </c>
       <c r="AO94" t="s" s="2">
         <v>79</v>
@@ -13819,10 +13812,10 @@
     </row>
     <row r="95" hidden="true">
       <c r="A95" t="s" s="2">
-        <v>628</v>
+        <v>632</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>628</v>
+        <v>632</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -13836,7 +13829,7 @@
         <v>78</v>
       </c>
       <c r="H95" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="I95" t="s" s="2">
         <v>79</v>
@@ -13845,18 +13838,20 @@
         <v>90</v>
       </c>
       <c r="K95" t="s" s="2">
-        <v>629</v>
+        <v>562</v>
       </c>
       <c r="L95" t="s" s="2">
-        <v>630</v>
+        <v>633</v>
       </c>
       <c r="M95" t="s" s="2">
-        <v>631</v>
+        <v>633</v>
       </c>
       <c r="N95" t="s" s="2">
-        <v>632</v>
-      </c>
-      <c r="O95" s="2"/>
+        <v>634</v>
+      </c>
+      <c r="O95" t="s" s="2">
+        <v>635</v>
+      </c>
       <c r="P95" t="s" s="2">
         <v>79</v>
       </c>
@@ -13904,7 +13899,7 @@
         <v>79</v>
       </c>
       <c r="AF95" t="s" s="2">
-        <v>628</v>
+        <v>632</v>
       </c>
       <c r="AG95" t="s" s="2">
         <v>77</v>
@@ -13916,7 +13911,7 @@
         <v>101</v>
       </c>
       <c r="AJ95" t="s" s="2">
-        <v>227</v>
+        <v>636</v>
       </c>
       <c r="AK95" t="s" s="2">
         <v>79</v>
@@ -13925,10 +13920,10 @@
         <v>79</v>
       </c>
       <c r="AM95" t="s" s="2">
-        <v>626</v>
+        <v>637</v>
       </c>
       <c r="AN95" t="s" s="2">
-        <v>633</v>
+        <v>638</v>
       </c>
       <c r="AO95" t="s" s="2">
         <v>79</v>
@@ -13939,10 +13934,10 @@
     </row>
     <row r="96" hidden="true">
       <c r="A96" t="s" s="2">
-        <v>634</v>
+        <v>639</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>634</v>
+        <v>639</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
@@ -13953,32 +13948,28 @@
         <v>77</v>
       </c>
       <c r="G96" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="H96" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="I96" t="s" s="2">
         <v>79</v>
       </c>
       <c r="J96" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="K96" t="s" s="2">
-        <v>564</v>
+        <v>105</v>
       </c>
       <c r="L96" t="s" s="2">
-        <v>635</v>
+        <v>106</v>
       </c>
       <c r="M96" t="s" s="2">
-        <v>635</v>
-      </c>
-      <c r="N96" t="s" s="2">
-        <v>636</v>
-      </c>
-      <c r="O96" t="s" s="2">
-        <v>637</v>
-      </c>
+        <v>107</v>
+      </c>
+      <c r="N96" s="2"/>
+      <c r="O96" s="2"/>
       <c r="P96" t="s" s="2">
         <v>79</v>
       </c>
@@ -14026,19 +14017,19 @@
         <v>79</v>
       </c>
       <c r="AF96" t="s" s="2">
-        <v>634</v>
+        <v>108</v>
       </c>
       <c r="AG96" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH96" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="AI96" t="s" s="2">
-        <v>101</v>
+        <v>79</v>
       </c>
       <c r="AJ96" t="s" s="2">
-        <v>638</v>
+        <v>79</v>
       </c>
       <c r="AK96" t="s" s="2">
         <v>79</v>
@@ -14047,10 +14038,10 @@
         <v>79</v>
       </c>
       <c r="AM96" t="s" s="2">
-        <v>639</v>
+        <v>79</v>
       </c>
       <c r="AN96" t="s" s="2">
-        <v>640</v>
+        <v>109</v>
       </c>
       <c r="AO96" t="s" s="2">
         <v>79</v>
@@ -14061,21 +14052,21 @@
     </row>
     <row r="97" hidden="true">
       <c r="A97" t="s" s="2">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
-        <v>79</v>
+        <v>111</v>
       </c>
       <c r="E97" s="2"/>
       <c r="F97" t="s" s="2">
         <v>77</v>
       </c>
       <c r="G97" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="H97" t="s" s="2">
         <v>79</v>
@@ -14087,15 +14078,17 @@
         <v>79</v>
       </c>
       <c r="K97" t="s" s="2">
-        <v>104</v>
+        <v>112</v>
       </c>
       <c r="L97" t="s" s="2">
-        <v>105</v>
+        <v>113</v>
       </c>
       <c r="M97" t="s" s="2">
-        <v>106</v>
-      </c>
-      <c r="N97" s="2"/>
+        <v>114</v>
+      </c>
+      <c r="N97" t="s" s="2">
+        <v>115</v>
+      </c>
       <c r="O97" s="2"/>
       <c r="P97" t="s" s="2">
         <v>79</v>
@@ -14132,31 +14125,31 @@
         <v>79</v>
       </c>
       <c r="AB97" t="s" s="2">
-        <v>79</v>
+        <v>116</v>
       </c>
       <c r="AC97" t="s" s="2">
-        <v>79</v>
+        <v>117</v>
       </c>
       <c r="AD97" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AE97" t="s" s="2">
-        <v>79</v>
+        <v>118</v>
       </c>
       <c r="AF97" t="s" s="2">
-        <v>107</v>
+        <v>119</v>
       </c>
       <c r="AG97" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH97" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="AI97" t="s" s="2">
-        <v>79</v>
+        <v>101</v>
       </c>
       <c r="AJ97" t="s" s="2">
-        <v>79</v>
+        <v>120</v>
       </c>
       <c r="AK97" t="s" s="2">
         <v>79</v>
@@ -14168,7 +14161,7 @@
         <v>79</v>
       </c>
       <c r="AN97" t="s" s="2">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="AO97" t="s" s="2">
         <v>79</v>
@@ -14179,14 +14172,14 @@
     </row>
     <row r="98" hidden="true">
       <c r="A98" t="s" s="2">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
-        <v>110</v>
+        <v>573</v>
       </c>
       <c r="E98" s="2"/>
       <c r="F98" t="s" s="2">
@@ -14199,24 +14192,26 @@
         <v>79</v>
       </c>
       <c r="I98" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="J98" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="K98" t="s" s="2">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="L98" t="s" s="2">
-        <v>112</v>
+        <v>574</v>
       </c>
       <c r="M98" t="s" s="2">
-        <v>113</v>
+        <v>575</v>
       </c>
       <c r="N98" t="s" s="2">
-        <v>114</v>
-      </c>
-      <c r="O98" s="2"/>
+        <v>115</v>
+      </c>
+      <c r="O98" t="s" s="2">
+        <v>207</v>
+      </c>
       <c r="P98" t="s" s="2">
         <v>79</v>
       </c>
@@ -14252,19 +14247,19 @@
         <v>79</v>
       </c>
       <c r="AB98" t="s" s="2">
-        <v>115</v>
+        <v>79</v>
       </c>
       <c r="AC98" t="s" s="2">
-        <v>116</v>
+        <v>79</v>
       </c>
       <c r="AD98" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AE98" t="s" s="2">
-        <v>117</v>
+        <v>79</v>
       </c>
       <c r="AF98" t="s" s="2">
-        <v>118</v>
+        <v>576</v>
       </c>
       <c r="AG98" t="s" s="2">
         <v>77</v>
@@ -14276,7 +14271,7 @@
         <v>101</v>
       </c>
       <c r="AJ98" t="s" s="2">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="AK98" t="s" s="2">
         <v>79</v>
@@ -14288,7 +14283,7 @@
         <v>79</v>
       </c>
       <c r="AN98" t="s" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="AO98" t="s" s="2">
         <v>79</v>
@@ -14299,45 +14294,45 @@
     </row>
     <row r="99" hidden="true">
       <c r="A99" t="s" s="2">
-        <v>643</v>
+        <v>642</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>643</v>
+        <v>642</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
-        <v>575</v>
+        <v>79</v>
       </c>
       <c r="E99" s="2"/>
       <c r="F99" t="s" s="2">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="G99" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="H99" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="I99" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="J99" t="s" s="2">
         <v>90</v>
       </c>
       <c r="K99" t="s" s="2">
-        <v>111</v>
+        <v>252</v>
       </c>
       <c r="L99" t="s" s="2">
-        <v>576</v>
+        <v>643</v>
       </c>
       <c r="M99" t="s" s="2">
-        <v>577</v>
+        <v>644</v>
       </c>
       <c r="N99" t="s" s="2">
-        <v>114</v>
+        <v>645</v>
       </c>
       <c r="O99" t="s" s="2">
-        <v>209</v>
+        <v>646</v>
       </c>
       <c r="P99" t="s" s="2">
         <v>79</v>
@@ -14362,13 +14357,13 @@
         <v>79</v>
       </c>
       <c r="X99" t="s" s="2">
-        <v>79</v>
+        <v>148</v>
       </c>
       <c r="Y99" t="s" s="2">
-        <v>79</v>
+        <v>345</v>
       </c>
       <c r="Z99" t="s" s="2">
-        <v>79</v>
+        <v>346</v>
       </c>
       <c r="AA99" t="s" s="2">
         <v>79</v>
@@ -14386,34 +14381,34 @@
         <v>79</v>
       </c>
       <c r="AF99" t="s" s="2">
-        <v>578</v>
+        <v>642</v>
       </c>
       <c r="AG99" t="s" s="2">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="AH99" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="AI99" t="s" s="2">
         <v>101</v>
       </c>
       <c r="AJ99" t="s" s="2">
-        <v>119</v>
+        <v>102</v>
       </c>
       <c r="AK99" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL99" t="s" s="2">
-        <v>79</v>
+        <v>647</v>
       </c>
       <c r="AM99" t="s" s="2">
-        <v>79</v>
+        <v>349</v>
       </c>
       <c r="AN99" t="s" s="2">
-        <v>102</v>
+        <v>350</v>
       </c>
       <c r="AO99" t="s" s="2">
-        <v>79</v>
+        <v>351</v>
       </c>
       <c r="AP99" t="s" s="2">
         <v>79</v>
@@ -14421,10 +14416,10 @@
     </row>
     <row r="100" hidden="true">
       <c r="A100" t="s" s="2">
-        <v>644</v>
+        <v>648</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>644</v>
+        <v>648</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
@@ -14432,7 +14427,7 @@
       </c>
       <c r="E100" s="2"/>
       <c r="F100" t="s" s="2">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="G100" t="s" s="2">
         <v>89</v>
@@ -14447,19 +14442,19 @@
         <v>90</v>
       </c>
       <c r="K100" t="s" s="2">
-        <v>254</v>
+        <v>649</v>
       </c>
       <c r="L100" t="s" s="2">
-        <v>645</v>
+        <v>650</v>
       </c>
       <c r="M100" t="s" s="2">
-        <v>646</v>
+        <v>651</v>
       </c>
       <c r="N100" t="s" s="2">
-        <v>647</v>
+        <v>652</v>
       </c>
       <c r="O100" t="s" s="2">
-        <v>648</v>
+        <v>413</v>
       </c>
       <c r="P100" t="s" s="2">
         <v>79</v>
@@ -14484,13 +14479,13 @@
         <v>79</v>
       </c>
       <c r="X100" t="s" s="2">
-        <v>150</v>
+        <v>243</v>
       </c>
       <c r="Y100" t="s" s="2">
-        <v>347</v>
+        <v>653</v>
       </c>
       <c r="Z100" t="s" s="2">
-        <v>348</v>
+        <v>654</v>
       </c>
       <c r="AA100" t="s" s="2">
         <v>79</v>
@@ -14508,45 +14503,45 @@
         <v>79</v>
       </c>
       <c r="AF100" t="s" s="2">
-        <v>644</v>
+        <v>648</v>
       </c>
       <c r="AG100" t="s" s="2">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="AH100" t="s" s="2">
         <v>89</v>
       </c>
       <c r="AI100" t="s" s="2">
-        <v>101</v>
+        <v>655</v>
       </c>
       <c r="AJ100" t="s" s="2">
-        <v>125</v>
+        <v>102</v>
       </c>
       <c r="AK100" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL100" t="s" s="2">
-        <v>649</v>
+        <v>656</v>
       </c>
       <c r="AM100" t="s" s="2">
-        <v>351</v>
+        <v>418</v>
       </c>
       <c r="AN100" t="s" s="2">
-        <v>352</v>
+        <v>419</v>
       </c>
       <c r="AO100" t="s" s="2">
-        <v>353</v>
+        <v>79</v>
       </c>
       <c r="AP100" t="s" s="2">
-        <v>79</v>
+        <v>420</v>
       </c>
     </row>
     <row r="101" hidden="true">
       <c r="A101" t="s" s="2">
-        <v>650</v>
+        <v>657</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>650</v>
+        <v>657</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
@@ -14566,22 +14561,22 @@
         <v>79</v>
       </c>
       <c r="J101" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="K101" t="s" s="2">
-        <v>651</v>
+        <v>252</v>
       </c>
       <c r="L101" t="s" s="2">
-        <v>652</v>
+        <v>658</v>
       </c>
       <c r="M101" t="s" s="2">
-        <v>653</v>
+        <v>659</v>
       </c>
       <c r="N101" t="s" s="2">
-        <v>654</v>
+        <v>660</v>
       </c>
       <c r="O101" t="s" s="2">
-        <v>415</v>
+        <v>479</v>
       </c>
       <c r="P101" t="s" s="2">
         <v>79</v>
@@ -14606,13 +14601,13 @@
         <v>79</v>
       </c>
       <c r="X101" t="s" s="2">
-        <v>245</v>
+        <v>148</v>
       </c>
       <c r="Y101" t="s" s="2">
-        <v>655</v>
+        <v>480</v>
       </c>
       <c r="Z101" t="s" s="2">
-        <v>656</v>
+        <v>481</v>
       </c>
       <c r="AA101" t="s" s="2">
         <v>79</v>
@@ -14630,7 +14625,7 @@
         <v>79</v>
       </c>
       <c r="AF101" t="s" s="2">
-        <v>650</v>
+        <v>657</v>
       </c>
       <c r="AG101" t="s" s="2">
         <v>77</v>
@@ -14639,50 +14634,50 @@
         <v>89</v>
       </c>
       <c r="AI101" t="s" s="2">
-        <v>657</v>
+        <v>661</v>
       </c>
       <c r="AJ101" t="s" s="2">
-        <v>125</v>
+        <v>102</v>
       </c>
       <c r="AK101" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL101" t="s" s="2">
-        <v>658</v>
+        <v>79</v>
       </c>
       <c r="AM101" t="s" s="2">
-        <v>420</v>
+        <v>103</v>
       </c>
       <c r="AN101" t="s" s="2">
-        <v>421</v>
+        <v>483</v>
       </c>
       <c r="AO101" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AP101" t="s" s="2">
-        <v>422</v>
+        <v>79</v>
       </c>
     </row>
     <row r="102" hidden="true">
       <c r="A102" t="s" s="2">
-        <v>659</v>
+        <v>662</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>659</v>
+        <v>662</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
-        <v>79</v>
+        <v>496</v>
       </c>
       <c r="E102" s="2"/>
       <c r="F102" t="s" s="2">
         <v>77</v>
       </c>
       <c r="G102" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="H102" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="I102" t="s" s="2">
         <v>79</v>
@@ -14691,19 +14686,19 @@
         <v>79</v>
       </c>
       <c r="K102" t="s" s="2">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="L102" t="s" s="2">
-        <v>660</v>
+        <v>497</v>
       </c>
       <c r="M102" t="s" s="2">
-        <v>661</v>
+        <v>498</v>
       </c>
       <c r="N102" t="s" s="2">
-        <v>662</v>
+        <v>499</v>
       </c>
       <c r="O102" t="s" s="2">
-        <v>481</v>
+        <v>500</v>
       </c>
       <c r="P102" t="s" s="2">
         <v>79</v>
@@ -14728,13 +14723,13 @@
         <v>79</v>
       </c>
       <c r="X102" t="s" s="2">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="Y102" t="s" s="2">
-        <v>482</v>
+        <v>501</v>
       </c>
       <c r="Z102" t="s" s="2">
-        <v>483</v>
+        <v>502</v>
       </c>
       <c r="AA102" t="s" s="2">
         <v>79</v>
@@ -14752,49 +14747,49 @@
         <v>79</v>
       </c>
       <c r="AF102" t="s" s="2">
-        <v>659</v>
+        <v>662</v>
       </c>
       <c r="AG102" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH102" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="AI102" t="s" s="2">
-        <v>663</v>
+        <v>101</v>
       </c>
       <c r="AJ102" t="s" s="2">
-        <v>125</v>
+        <v>102</v>
       </c>
       <c r="AK102" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL102" t="s" s="2">
-        <v>79</v>
+        <v>503</v>
       </c>
       <c r="AM102" t="s" s="2">
-        <v>102</v>
+        <v>504</v>
       </c>
       <c r="AN102" t="s" s="2">
-        <v>485</v>
+        <v>505</v>
       </c>
       <c r="AO102" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AP102" t="s" s="2">
-        <v>79</v>
+        <v>506</v>
       </c>
     </row>
     <row r="103" hidden="true">
       <c r="A103" t="s" s="2">
-        <v>664</v>
+        <v>663</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>664</v>
+        <v>663</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
-        <v>498</v>
+        <v>79</v>
       </c>
       <c r="E103" s="2"/>
       <c r="F103" t="s" s="2">
@@ -14813,19 +14808,19 @@
         <v>79</v>
       </c>
       <c r="K103" t="s" s="2">
-        <v>254</v>
+        <v>80</v>
       </c>
       <c r="L103" t="s" s="2">
-        <v>499</v>
+        <v>664</v>
       </c>
       <c r="M103" t="s" s="2">
-        <v>500</v>
+        <v>665</v>
       </c>
       <c r="N103" t="s" s="2">
-        <v>501</v>
+        <v>565</v>
       </c>
       <c r="O103" t="s" s="2">
-        <v>502</v>
+        <v>566</v>
       </c>
       <c r="P103" t="s" s="2">
         <v>79</v>
@@ -14850,13 +14845,13 @@
         <v>79</v>
       </c>
       <c r="X103" t="s" s="2">
-        <v>150</v>
+        <v>79</v>
       </c>
       <c r="Y103" t="s" s="2">
-        <v>503</v>
+        <v>79</v>
       </c>
       <c r="Z103" t="s" s="2">
-        <v>504</v>
+        <v>79</v>
       </c>
       <c r="AA103" t="s" s="2">
         <v>79</v>
@@ -14874,7 +14869,7 @@
         <v>79</v>
       </c>
       <c r="AF103" t="s" s="2">
-        <v>664</v>
+        <v>663</v>
       </c>
       <c r="AG103" t="s" s="2">
         <v>77</v>
@@ -14883,154 +14878,32 @@
         <v>78</v>
       </c>
       <c r="AI103" t="s" s="2">
-        <v>101</v>
+        <v>79</v>
       </c>
       <c r="AJ103" t="s" s="2">
-        <v>125</v>
+        <v>79</v>
       </c>
       <c r="AK103" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL103" t="s" s="2">
-        <v>505</v>
+        <v>79</v>
       </c>
       <c r="AM103" t="s" s="2">
-        <v>506</v>
+        <v>568</v>
       </c>
       <c r="AN103" t="s" s="2">
-        <v>507</v>
+        <v>569</v>
       </c>
       <c r="AO103" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AP103" t="s" s="2">
-        <v>508</v>
-      </c>
-    </row>
-    <row r="104" hidden="true">
-      <c r="A104" t="s" s="2">
-        <v>665</v>
-      </c>
-      <c r="B104" t="s" s="2">
-        <v>665</v>
-      </c>
-      <c r="C104" s="2"/>
-      <c r="D104" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="E104" s="2"/>
-      <c r="F104" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="G104" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="H104" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="I104" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="J104" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="K104" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="L104" t="s" s="2">
-        <v>666</v>
-      </c>
-      <c r="M104" t="s" s="2">
-        <v>667</v>
-      </c>
-      <c r="N104" t="s" s="2">
-        <v>567</v>
-      </c>
-      <c r="O104" t="s" s="2">
-        <v>568</v>
-      </c>
-      <c r="P104" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Q104" s="2"/>
-      <c r="R104" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="S104" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="T104" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="U104" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="V104" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="W104" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="X104" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Y104" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Z104" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AA104" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AB104" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC104" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AD104" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AE104" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AF104" t="s" s="2">
-        <v>665</v>
-      </c>
-      <c r="AG104" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AH104" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AI104" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AJ104" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AK104" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AL104" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AM104" t="s" s="2">
-        <v>570</v>
-      </c>
-      <c r="AN104" t="s" s="2">
-        <v>571</v>
-      </c>
-      <c r="AO104" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AP104" t="s" s="2">
         <v>79</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AP104">
+  <autoFilter ref="A1:AP103">
     <filterColumn colId="6">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -15040,7 +14913,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI103">
+  <conditionalFormatting sqref="A2:AI102">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>
